--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/10,26/27,10,26 ПОКОМ КИ/дв 27,10,26 днрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/10,26/27,10,26 ПОКОМ КИ/дв 27,10,26 днрсч пок ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\10,26\27,10,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827E5452-2931-4338-A409-FB4B8D7D30B4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2613448-7406-4915-82AC-F224BD56807D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AL$131</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1275,13 +1275,13 @@
   <dimension ref="A1:AV496"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.140625" customWidth="1"/>
+    <col min="1" max="1" width="44.5703125" customWidth="1"/>
     <col min="2" max="2" width="3" customWidth="1"/>
     <col min="3" max="4" width="6" customWidth="1"/>
     <col min="5" max="6" width="7" customWidth="1"/>
     <col min="7" max="7" width="5" style="6" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" customWidth="1"/>
+    <col min="9" max="9" width="3.85546875" customWidth="1"/>
     <col min="10" max="10" width="1" customWidth="1"/>
     <col min="11" max="22" width="7" customWidth="1"/>
     <col min="23" max="23" width="7" style="23" customWidth="1"/>
@@ -1290,7 +1290,8 @@
     <col min="27" max="36" width="6.85546875" customWidth="1"/>
     <col min="37" max="37" width="12.28515625" customWidth="1"/>
     <col min="38" max="39" width="7" customWidth="1"/>
-    <col min="40" max="48" width="8" customWidth="1"/>
+    <col min="40" max="40" width="8" style="6" customWidth="1"/>
+    <col min="41" max="48" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:48" x14ac:dyDescent="0.25">
@@ -1343,7 +1344,7 @@
         <f>AM2-AM5</f>
         <v>-57</v>
       </c>
-      <c r="AN1" s="1"/>
+      <c r="AN1" s="7"/>
       <c r="AO1" s="1"/>
       <c r="AP1" s="1"/>
       <c r="AQ1" s="1"/>
@@ -1401,7 +1402,7 @@
       <c r="AM2" s="1">
         <v>17600</v>
       </c>
-      <c r="AN2" s="1"/>
+      <c r="AN2" s="7"/>
       <c r="AO2" s="1"/>
       <c r="AP2" s="1"/>
       <c r="AQ2" s="1"/>
@@ -1529,7 +1530,7 @@
       <c r="AM3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AN3" s="1"/>
+      <c r="AN3" s="7"/>
       <c r="AO3" s="1"/>
       <c r="AP3" s="1"/>
       <c r="AQ3" s="1"/>
@@ -1617,7 +1618,7 @@
       <c r="AM4" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="AN4" s="1"/>
+      <c r="AN4" s="7"/>
       <c r="AO4" s="1"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="1"/>
@@ -1748,7 +1749,7 @@
         <f>SUM(AM6:AM496)</f>
         <v>17657</v>
       </c>
-      <c r="AN5" s="1"/>
+      <c r="AN5" s="7"/>
       <c r="AO5" s="1"/>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="1"/>
@@ -1876,7 +1877,7 @@
         <f>ROUND(G6*V6,0)</f>
         <v>1020</v>
       </c>
-      <c r="AN6" s="1"/>
+      <c r="AN6" s="7"/>
       <c r="AO6" s="1"/>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="1"/>
@@ -2005,7 +2006,7 @@
         <f t="shared" ref="AM7:AM70" si="12">ROUND(G7*V7,0)</f>
         <v>643</v>
       </c>
-      <c r="AN7" s="1"/>
+      <c r="AN7" s="7"/>
       <c r="AO7" s="1"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="1"/>
@@ -2136,7 +2137,7 @@
         <f t="shared" si="12"/>
         <v>1209</v>
       </c>
-      <c r="AN8" s="1"/>
+      <c r="AN8" s="7"/>
       <c r="AO8" s="1"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="1"/>
@@ -2257,7 +2258,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN9" s="1"/>
+      <c r="AN9" s="7"/>
       <c r="AO9" s="1"/>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="1"/>
@@ -2389,7 +2390,7 @@
         <f t="shared" si="12"/>
         <v>198</v>
       </c>
-      <c r="AN10" s="1"/>
+      <c r="AN10" s="7"/>
       <c r="AO10" s="1"/>
       <c r="AP10" s="1"/>
       <c r="AQ10" s="1"/>
@@ -2516,7 +2517,7 @@
         <f t="shared" si="12"/>
         <v>744</v>
       </c>
-      <c r="AN11" s="1"/>
+      <c r="AN11" s="7"/>
       <c r="AO11" s="1"/>
       <c r="AP11" s="1"/>
       <c r="AQ11" s="1"/>
@@ -2635,7 +2636,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN12" s="1"/>
+      <c r="AN12" s="7"/>
       <c r="AO12" s="1"/>
       <c r="AP12" s="1"/>
       <c r="AQ12" s="1"/>
@@ -2754,7 +2755,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN13" s="1"/>
+      <c r="AN13" s="7"/>
       <c r="AO13" s="1"/>
       <c r="AP13" s="1"/>
       <c r="AQ13" s="1"/>
@@ -2875,7 +2876,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN14" s="1"/>
+      <c r="AN14" s="7"/>
       <c r="AO14" s="1"/>
       <c r="AP14" s="1"/>
       <c r="AQ14" s="1"/>
@@ -3011,7 +3012,7 @@
         <f t="shared" si="12"/>
         <v>770</v>
       </c>
-      <c r="AN15" s="1"/>
+      <c r="AN15" s="7"/>
       <c r="AO15" s="1"/>
       <c r="AP15" s="1"/>
       <c r="AQ15" s="1"/>
@@ -3142,7 +3143,7 @@
         <f t="shared" si="12"/>
         <v>718</v>
       </c>
-      <c r="AN16" s="1"/>
+      <c r="AN16" s="7"/>
       <c r="AO16" s="1"/>
       <c r="AP16" s="1"/>
       <c r="AQ16" s="1"/>
@@ -3270,7 +3271,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN17" s="1"/>
+      <c r="AN17" s="7"/>
       <c r="AO17" s="1"/>
       <c r="AP17" s="1"/>
       <c r="AQ17" s="1"/>
@@ -3381,7 +3382,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN18" s="1"/>
+      <c r="AN18" s="7"/>
       <c r="AO18" s="1"/>
       <c r="AP18" s="1"/>
       <c r="AQ18" s="1"/>
@@ -3500,7 +3501,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN19" s="1"/>
+      <c r="AN19" s="7"/>
       <c r="AO19" s="1"/>
       <c r="AP19" s="1"/>
       <c r="AQ19" s="1"/>
@@ -3631,7 +3632,7 @@
         <f t="shared" si="12"/>
         <v>550</v>
       </c>
-      <c r="AN20" s="1"/>
+      <c r="AN20" s="7"/>
       <c r="AO20" s="1"/>
       <c r="AP20" s="1"/>
       <c r="AQ20" s="1"/>
@@ -3753,7 +3754,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN21" s="1"/>
+      <c r="AN21" s="7"/>
       <c r="AO21" s="1"/>
       <c r="AP21" s="1"/>
       <c r="AQ21" s="1"/>
@@ -3884,7 +3885,7 @@
         <f t="shared" si="12"/>
         <v>413</v>
       </c>
-      <c r="AN22" s="1"/>
+      <c r="AN22" s="7"/>
       <c r="AO22" s="1"/>
       <c r="AP22" s="1"/>
       <c r="AQ22" s="1"/>
@@ -3993,7 +3994,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN23" s="1"/>
+      <c r="AN23" s="7"/>
       <c r="AO23" s="1"/>
       <c r="AP23" s="1"/>
       <c r="AQ23" s="1"/>
@@ -4122,7 +4123,7 @@
         <f t="shared" si="12"/>
         <v>1540</v>
       </c>
-      <c r="AN24" s="1"/>
+      <c r="AN24" s="7"/>
       <c r="AO24" s="1"/>
       <c r="AP24" s="1"/>
       <c r="AQ24" s="1"/>
@@ -4233,7 +4234,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN25" s="1"/>
+      <c r="AN25" s="7"/>
       <c r="AO25" s="1"/>
       <c r="AP25" s="1"/>
       <c r="AQ25" s="1"/>
@@ -4355,7 +4356,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN26" s="1"/>
+      <c r="AN26" s="7"/>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
       <c r="AQ26" s="1"/>
@@ -4469,7 +4470,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN27" s="1"/>
+      <c r="AN27" s="7"/>
       <c r="AO27" s="1"/>
       <c r="AP27" s="1"/>
       <c r="AQ27" s="1"/>
@@ -4578,7 +4579,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN28" s="1"/>
+      <c r="AN28" s="7"/>
       <c r="AO28" s="1"/>
       <c r="AP28" s="1"/>
       <c r="AQ28" s="1"/>
@@ -4709,7 +4710,7 @@
         <f t="shared" si="12"/>
         <v>393</v>
       </c>
-      <c r="AN29" s="1"/>
+      <c r="AN29" s="7"/>
       <c r="AO29" s="1"/>
       <c r="AP29" s="1"/>
       <c r="AQ29" s="1"/>
@@ -4840,7 +4841,7 @@
         <f t="shared" si="12"/>
         <v>1525</v>
       </c>
-      <c r="AN30" s="1"/>
+      <c r="AN30" s="7"/>
       <c r="AO30" s="1"/>
       <c r="AP30" s="1"/>
       <c r="AQ30" s="1"/>
@@ -4949,7 +4950,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN31" s="1"/>
+      <c r="AN31" s="7"/>
       <c r="AO31" s="1"/>
       <c r="AP31" s="1"/>
       <c r="AQ31" s="1"/>
@@ -5063,7 +5064,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN32" s="1"/>
+      <c r="AN32" s="7"/>
       <c r="AO32" s="1"/>
       <c r="AP32" s="1"/>
       <c r="AQ32" s="1"/>
@@ -5172,7 +5173,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN33" s="1"/>
+      <c r="AN33" s="7"/>
       <c r="AO33" s="1"/>
       <c r="AP33" s="1"/>
       <c r="AQ33" s="1"/>
@@ -5281,7 +5282,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN34" s="1"/>
+      <c r="AN34" s="7"/>
       <c r="AO34" s="1"/>
       <c r="AP34" s="1"/>
       <c r="AQ34" s="1"/>
@@ -5412,7 +5413,7 @@
         <f t="shared" si="12"/>
         <v>534</v>
       </c>
-      <c r="AN35" s="1"/>
+      <c r="AN35" s="7"/>
       <c r="AO35" s="1"/>
       <c r="AP35" s="1"/>
       <c r="AQ35" s="1"/>
@@ -5535,7 +5536,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN36" s="1"/>
+      <c r="AN36" s="7"/>
       <c r="AO36" s="1"/>
       <c r="AP36" s="1"/>
       <c r="AQ36" s="1"/>
@@ -5664,7 +5665,7 @@
         <f t="shared" si="12"/>
         <v>150</v>
       </c>
-      <c r="AN37" s="1"/>
+      <c r="AN37" s="7"/>
       <c r="AO37" s="1"/>
       <c r="AP37" s="1"/>
       <c r="AQ37" s="1"/>
@@ -5783,7 +5784,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN38" s="1"/>
+      <c r="AN38" s="7"/>
       <c r="AO38" s="1"/>
       <c r="AP38" s="1"/>
       <c r="AQ38" s="1"/>
@@ -5902,7 +5903,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN39" s="1"/>
+      <c r="AN39" s="7"/>
       <c r="AO39" s="1"/>
       <c r="AP39" s="1"/>
       <c r="AQ39" s="1"/>
@@ -6023,7 +6024,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN40" s="1"/>
+      <c r="AN40" s="7"/>
       <c r="AO40" s="1"/>
       <c r="AP40" s="1"/>
       <c r="AQ40" s="1"/>
@@ -6138,7 +6139,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN41" s="1"/>
+      <c r="AN41" s="7"/>
       <c r="AO41" s="1"/>
       <c r="AP41" s="1"/>
       <c r="AQ41" s="1"/>
@@ -6260,7 +6261,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN42" s="1"/>
+      <c r="AN42" s="7"/>
       <c r="AO42" s="1"/>
       <c r="AP42" s="1"/>
       <c r="AQ42" s="1"/>
@@ -6385,7 +6386,7 @@
         <f t="shared" si="12"/>
         <v>97</v>
       </c>
-      <c r="AN43" s="1"/>
+      <c r="AN43" s="7"/>
       <c r="AO43" s="1"/>
       <c r="AP43" s="1"/>
       <c r="AQ43" s="1"/>
@@ -6510,7 +6511,7 @@
         <f t="shared" si="12"/>
         <v>225</v>
       </c>
-      <c r="AN44" s="1"/>
+      <c r="AN44" s="7"/>
       <c r="AO44" s="1"/>
       <c r="AP44" s="1"/>
       <c r="AQ44" s="1"/>
@@ -6631,7 +6632,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN45" s="1"/>
+      <c r="AN45" s="7"/>
       <c r="AO45" s="1"/>
       <c r="AP45" s="1"/>
       <c r="AQ45" s="1"/>
@@ -6754,7 +6755,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN46" s="1"/>
+      <c r="AN46" s="7"/>
       <c r="AO46" s="1"/>
       <c r="AP46" s="1"/>
       <c r="AQ46" s="1"/>
@@ -6876,7 +6877,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN47" s="1"/>
+      <c r="AN47" s="7"/>
       <c r="AO47" s="1"/>
       <c r="AP47" s="1"/>
       <c r="AQ47" s="1"/>
@@ -6998,7 +6999,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN48" s="1"/>
+      <c r="AN48" s="7"/>
       <c r="AO48" s="1"/>
       <c r="AP48" s="1"/>
       <c r="AQ48" s="1"/>
@@ -7119,7 +7120,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN49" s="1"/>
+      <c r="AN49" s="7"/>
       <c r="AO49" s="1"/>
       <c r="AP49" s="1"/>
       <c r="AQ49" s="1"/>
@@ -7228,7 +7229,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN50" s="1"/>
+      <c r="AN50" s="7"/>
       <c r="AO50" s="1"/>
       <c r="AP50" s="1"/>
       <c r="AQ50" s="1"/>
@@ -7355,7 +7356,10 @@
         <f t="shared" si="12"/>
         <v>140</v>
       </c>
-      <c r="AN51" s="1"/>
+      <c r="AN51" s="7">
+        <f>R51/AA51</f>
+        <v>2.0132450331125828</v>
+      </c>
       <c r="AO51" s="1"/>
       <c r="AP51" s="1"/>
       <c r="AQ51" s="1"/>
@@ -7482,7 +7486,7 @@
         <f t="shared" si="12"/>
         <v>102</v>
       </c>
-      <c r="AN52" s="1"/>
+      <c r="AN52" s="7"/>
       <c r="AO52" s="1"/>
       <c r="AP52" s="1"/>
       <c r="AQ52" s="1"/>
@@ -7591,7 +7595,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN53" s="1"/>
+      <c r="AN53" s="7"/>
       <c r="AO53" s="1"/>
       <c r="AP53" s="1"/>
       <c r="AQ53" s="1"/>
@@ -7715,7 +7719,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN54" s="1"/>
+      <c r="AN54" s="7"/>
       <c r="AO54" s="1"/>
       <c r="AP54" s="1"/>
       <c r="AQ54" s="1"/>
@@ -7838,7 +7842,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN55" s="1"/>
+      <c r="AN55" s="7"/>
       <c r="AO55" s="1"/>
       <c r="AP55" s="1"/>
       <c r="AQ55" s="1"/>
@@ -7962,7 +7966,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN56" s="1"/>
+      <c r="AN56" s="7"/>
       <c r="AO56" s="1"/>
       <c r="AP56" s="1"/>
       <c r="AQ56" s="1"/>
@@ -8085,7 +8089,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN57" s="1"/>
+      <c r="AN57" s="7"/>
       <c r="AO57" s="1"/>
       <c r="AP57" s="1"/>
       <c r="AQ57" s="1"/>
@@ -8207,7 +8211,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN58" s="1"/>
+      <c r="AN58" s="7"/>
       <c r="AO58" s="1"/>
       <c r="AP58" s="1"/>
       <c r="AQ58" s="1"/>
@@ -8329,7 +8333,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN59" s="1"/>
+      <c r="AN59" s="7"/>
       <c r="AO59" s="1"/>
       <c r="AP59" s="1"/>
       <c r="AQ59" s="1"/>
@@ -8451,7 +8455,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN60" s="1"/>
+      <c r="AN60" s="7"/>
       <c r="AO60" s="1"/>
       <c r="AP60" s="1"/>
       <c r="AQ60" s="1"/>
@@ -8572,7 +8576,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN61" s="1"/>
+      <c r="AN61" s="7"/>
       <c r="AO61" s="1"/>
       <c r="AP61" s="1"/>
       <c r="AQ61" s="1"/>
@@ -8705,7 +8709,7 @@
         <f t="shared" si="12"/>
         <v>138</v>
       </c>
-      <c r="AN62" s="1"/>
+      <c r="AN62" s="7"/>
       <c r="AO62" s="1"/>
       <c r="AP62" s="1"/>
       <c r="AQ62" s="1"/>
@@ -8832,7 +8836,7 @@
         <f t="shared" si="12"/>
         <v>96</v>
       </c>
-      <c r="AN63" s="1"/>
+      <c r="AN63" s="7"/>
       <c r="AO63" s="1"/>
       <c r="AP63" s="1"/>
       <c r="AQ63" s="1"/>
@@ -8959,7 +8963,7 @@
         <f t="shared" si="12"/>
         <v>139</v>
       </c>
-      <c r="AN64" s="1"/>
+      <c r="AN64" s="7"/>
       <c r="AO64" s="1"/>
       <c r="AP64" s="1"/>
       <c r="AQ64" s="1"/>
@@ -9082,7 +9086,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN65" s="1"/>
+      <c r="AN65" s="7"/>
       <c r="AO65" s="1"/>
       <c r="AP65" s="1"/>
       <c r="AQ65" s="1"/>
@@ -9203,7 +9207,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN66" s="1"/>
+      <c r="AN66" s="7"/>
       <c r="AO66" s="1"/>
       <c r="AP66" s="1"/>
       <c r="AQ66" s="1"/>
@@ -9322,7 +9326,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN67" s="1"/>
+      <c r="AN67" s="7">
+        <f>R67/AB67</f>
+        <v>4.1816950071133396</v>
+      </c>
       <c r="AO67" s="1"/>
       <c r="AP67" s="1"/>
       <c r="AQ67" s="1"/>
@@ -9443,7 +9450,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN68" s="1"/>
+      <c r="AN68" s="7"/>
       <c r="AO68" s="1"/>
       <c r="AP68" s="1"/>
       <c r="AQ68" s="1"/>
@@ -9562,7 +9569,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN69" s="1"/>
+      <c r="AN69" s="7"/>
       <c r="AO69" s="1"/>
       <c r="AP69" s="1"/>
       <c r="AQ69" s="1"/>
@@ -9685,7 +9692,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN70" s="1"/>
+      <c r="AN70" s="7"/>
       <c r="AO70" s="1"/>
       <c r="AP70" s="1"/>
       <c r="AQ70" s="1"/>
@@ -9806,7 +9813,7 @@
         <f t="shared" ref="AM71:AM131" si="39">ROUND(G71*V71,0)</f>
         <v>0</v>
       </c>
-      <c r="AN71" s="1"/>
+      <c r="AN71" s="7"/>
       <c r="AO71" s="1"/>
       <c r="AP71" s="1"/>
       <c r="AQ71" s="1"/>
@@ -9927,7 +9934,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN72" s="1"/>
+      <c r="AN72" s="7"/>
       <c r="AO72" s="1"/>
       <c r="AP72" s="1"/>
       <c r="AQ72" s="1"/>
@@ -10044,7 +10051,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN73" s="1"/>
+      <c r="AN73" s="7"/>
       <c r="AO73" s="1"/>
       <c r="AP73" s="1"/>
       <c r="AQ73" s="1"/>
@@ -10153,7 +10160,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN74" s="1"/>
+      <c r="AN74" s="7"/>
       <c r="AO74" s="1"/>
       <c r="AP74" s="1"/>
       <c r="AQ74" s="1"/>
@@ -10275,7 +10282,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN75" s="1"/>
+      <c r="AN75" s="7"/>
       <c r="AO75" s="1"/>
       <c r="AP75" s="1"/>
       <c r="AQ75" s="1"/>
@@ -10397,7 +10404,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN76" s="1"/>
+      <c r="AN76" s="7"/>
       <c r="AO76" s="1"/>
       <c r="AP76" s="1"/>
       <c r="AQ76" s="1"/>
@@ -10518,7 +10525,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN77" s="1"/>
+      <c r="AN77" s="7"/>
       <c r="AO77" s="1"/>
       <c r="AP77" s="1"/>
       <c r="AQ77" s="1"/>
@@ -10642,7 +10649,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN78" s="1"/>
+      <c r="AN78" s="7"/>
       <c r="AO78" s="1"/>
       <c r="AP78" s="1"/>
       <c r="AQ78" s="1"/>
@@ -10764,7 +10771,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN79" s="1"/>
+      <c r="AN79" s="7"/>
       <c r="AO79" s="1"/>
       <c r="AP79" s="1"/>
       <c r="AQ79" s="1"/>
@@ -10883,7 +10890,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN80" s="1"/>
+      <c r="AN80" s="7"/>
       <c r="AO80" s="1"/>
       <c r="AP80" s="1"/>
       <c r="AQ80" s="1"/>
@@ -11009,7 +11016,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN81" s="1"/>
+      <c r="AN81" s="7"/>
       <c r="AO81" s="1"/>
       <c r="AP81" s="1"/>
       <c r="AQ81" s="1"/>
@@ -11130,7 +11137,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN82" s="1"/>
+      <c r="AN82" s="7"/>
       <c r="AO82" s="1"/>
       <c r="AP82" s="1"/>
       <c r="AQ82" s="1"/>
@@ -11251,7 +11258,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN83" s="1"/>
+      <c r="AN83" s="7"/>
       <c r="AO83" s="1"/>
       <c r="AP83" s="1"/>
       <c r="AQ83" s="1"/>
@@ -11360,7 +11367,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN84" s="1"/>
+      <c r="AN84" s="7"/>
       <c r="AO84" s="1"/>
       <c r="AP84" s="1"/>
       <c r="AQ84" s="1"/>
@@ -11489,7 +11496,7 @@
         <f t="shared" si="39"/>
         <v>1412</v>
       </c>
-      <c r="AN85" s="1"/>
+      <c r="AN85" s="7"/>
       <c r="AO85" s="1"/>
       <c r="AP85" s="1"/>
       <c r="AQ85" s="1"/>
@@ -11613,7 +11620,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN86" s="1"/>
+      <c r="AN86" s="7"/>
       <c r="AO86" s="1"/>
       <c r="AP86" s="1"/>
       <c r="AQ86" s="1"/>
@@ -11736,7 +11743,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN87" s="1"/>
+      <c r="AN87" s="7"/>
       <c r="AO87" s="1"/>
       <c r="AP87" s="1"/>
       <c r="AQ87" s="1"/>
@@ -11865,7 +11872,7 @@
         <f t="shared" si="39"/>
         <v>1196</v>
       </c>
-      <c r="AN88" s="1"/>
+      <c r="AN88" s="7"/>
       <c r="AO88" s="1"/>
       <c r="AP88" s="1"/>
       <c r="AQ88" s="1"/>
@@ -11994,7 +12001,7 @@
         <f t="shared" si="39"/>
         <v>1925</v>
       </c>
-      <c r="AN89" s="1"/>
+      <c r="AN89" s="7"/>
       <c r="AO89" s="1"/>
       <c r="AP89" s="1"/>
       <c r="AQ89" s="1"/>
@@ -12116,7 +12123,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN90" s="1"/>
+      <c r="AN90" s="7"/>
       <c r="AO90" s="1"/>
       <c r="AP90" s="1"/>
       <c r="AQ90" s="1"/>
@@ -12235,7 +12242,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN91" s="1"/>
+      <c r="AN91" s="7"/>
       <c r="AO91" s="1"/>
       <c r="AP91" s="1"/>
       <c r="AQ91" s="1"/>
@@ -12354,7 +12361,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN92" s="1"/>
+      <c r="AN92" s="7"/>
       <c r="AO92" s="1"/>
       <c r="AP92" s="1"/>
       <c r="AQ92" s="1"/>
@@ -12476,7 +12483,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN93" s="1"/>
+      <c r="AN93" s="7"/>
       <c r="AO93" s="1"/>
       <c r="AP93" s="1"/>
       <c r="AQ93" s="1"/>
@@ -12598,7 +12605,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN94" s="1"/>
+      <c r="AN94" s="7"/>
       <c r="AO94" s="1"/>
       <c r="AP94" s="1"/>
       <c r="AQ94" s="1"/>
@@ -12720,7 +12727,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN95" s="1"/>
+      <c r="AN95" s="7"/>
       <c r="AO95" s="1"/>
       <c r="AP95" s="1"/>
       <c r="AQ95" s="1"/>
@@ -12837,7 +12844,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN96" s="1"/>
+      <c r="AN96" s="7"/>
       <c r="AO96" s="1"/>
       <c r="AP96" s="1"/>
       <c r="AQ96" s="1"/>
@@ -12958,7 +12965,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN97" s="1"/>
+      <c r="AN97" s="7"/>
       <c r="AO97" s="1"/>
       <c r="AP97" s="1"/>
       <c r="AQ97" s="1"/>
@@ -13067,7 +13074,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN98" s="1"/>
+      <c r="AN98" s="7"/>
       <c r="AO98" s="1"/>
       <c r="AP98" s="1"/>
       <c r="AQ98" s="1"/>
@@ -13192,7 +13199,7 @@
         <f t="shared" si="39"/>
         <v>12</v>
       </c>
-      <c r="AN99" s="1"/>
+      <c r="AN99" s="7"/>
       <c r="AO99" s="1"/>
       <c r="AP99" s="1"/>
       <c r="AQ99" s="1"/>
@@ -13313,7 +13320,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN100" s="1"/>
+      <c r="AN100" s="7"/>
       <c r="AO100" s="1"/>
       <c r="AP100" s="1"/>
       <c r="AQ100" s="1"/>
@@ -13437,7 +13444,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN101" s="1"/>
+      <c r="AN101" s="7"/>
       <c r="AO101" s="1"/>
       <c r="AP101" s="1"/>
       <c r="AQ101" s="1"/>
@@ -13564,7 +13571,7 @@
         <f t="shared" si="39"/>
         <v>363</v>
       </c>
-      <c r="AN102" s="1"/>
+      <c r="AN102" s="7"/>
       <c r="AO102" s="1"/>
       <c r="AP102" s="1"/>
       <c r="AQ102" s="1"/>
@@ -13687,7 +13694,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN103" s="1"/>
+      <c r="AN103" s="7"/>
       <c r="AO103" s="1"/>
       <c r="AP103" s="1"/>
       <c r="AQ103" s="1"/>
@@ -13808,7 +13815,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN104" s="1"/>
+      <c r="AN104" s="7"/>
       <c r="AO104" s="1"/>
       <c r="AP104" s="1"/>
       <c r="AQ104" s="1"/>
@@ -13927,7 +13934,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN105" s="1"/>
+      <c r="AN105" s="7"/>
       <c r="AO105" s="1"/>
       <c r="AP105" s="1"/>
       <c r="AQ105" s="1"/>
@@ -14046,7 +14053,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN106" s="1"/>
+      <c r="AN106" s="7"/>
       <c r="AO106" s="1"/>
       <c r="AP106" s="1"/>
       <c r="AQ106" s="1"/>
@@ -14165,7 +14172,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN107" s="1"/>
+      <c r="AN107" s="7"/>
       <c r="AO107" s="1"/>
       <c r="AP107" s="1"/>
       <c r="AQ107" s="1"/>
@@ -14284,7 +14291,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN108" s="1"/>
+      <c r="AN108" s="7"/>
       <c r="AO108" s="1"/>
       <c r="AP108" s="1"/>
       <c r="AQ108" s="1"/>
@@ -14409,7 +14416,7 @@
         <f t="shared" si="39"/>
         <v>72</v>
       </c>
-      <c r="AN109" s="1"/>
+      <c r="AN109" s="7"/>
       <c r="AO109" s="1"/>
       <c r="AP109" s="1"/>
       <c r="AQ109" s="1"/>
@@ -14538,7 +14545,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN110" s="1"/>
+      <c r="AN110" s="7"/>
       <c r="AO110" s="1"/>
       <c r="AP110" s="1"/>
       <c r="AQ110" s="1"/>
@@ -14659,7 +14666,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN111" s="1"/>
+      <c r="AN111" s="7"/>
       <c r="AO111" s="1"/>
       <c r="AP111" s="1"/>
       <c r="AQ111" s="1"/>
@@ -14778,7 +14785,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN112" s="1"/>
+      <c r="AN112" s="7"/>
       <c r="AO112" s="1"/>
       <c r="AP112" s="1"/>
       <c r="AQ112" s="1"/>
@@ -14899,7 +14906,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN113" s="1"/>
+      <c r="AN113" s="7"/>
       <c r="AO113" s="1"/>
       <c r="AP113" s="1"/>
       <c r="AQ113" s="1"/>
@@ -15028,7 +15035,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN114" s="1"/>
+      <c r="AN114" s="7"/>
       <c r="AO114" s="1"/>
       <c r="AP114" s="1"/>
       <c r="AQ114" s="1"/>
@@ -15150,7 +15157,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN115" s="1"/>
+      <c r="AN115" s="7"/>
       <c r="AO115" s="1"/>
       <c r="AP115" s="1"/>
       <c r="AQ115" s="1"/>
@@ -15277,7 +15284,7 @@
         <f t="shared" si="39"/>
         <v>373</v>
       </c>
-      <c r="AN116" s="1"/>
+      <c r="AN116" s="7"/>
       <c r="AO116" s="1"/>
       <c r="AP116" s="1"/>
       <c r="AQ116" s="1"/>
@@ -15396,7 +15403,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN117" s="1"/>
+      <c r="AN117" s="7"/>
       <c r="AO117" s="1"/>
       <c r="AP117" s="1"/>
       <c r="AQ117" s="1"/>
@@ -15521,7 +15528,7 @@
         <f t="shared" si="39"/>
         <v>960</v>
       </c>
-      <c r="AN118" s="1"/>
+      <c r="AN118" s="7"/>
       <c r="AO118" s="1"/>
       <c r="AP118" s="1"/>
       <c r="AQ118" s="1"/>
@@ -15636,7 +15643,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN119" s="1"/>
+      <c r="AN119" s="7"/>
       <c r="AO119" s="1"/>
       <c r="AP119" s="1"/>
       <c r="AQ119" s="1"/>
@@ -15751,7 +15758,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN120" s="1"/>
+      <c r="AN120" s="7"/>
       <c r="AO120" s="1"/>
       <c r="AP120" s="1"/>
       <c r="AQ120" s="1"/>
@@ -15866,7 +15873,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN121" s="1"/>
+      <c r="AN121" s="7"/>
       <c r="AO121" s="1"/>
       <c r="AP121" s="1"/>
       <c r="AQ121" s="1"/>
@@ -15983,7 +15990,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN122" s="1"/>
+      <c r="AN122" s="7"/>
       <c r="AO122" s="1"/>
       <c r="AP122" s="1"/>
       <c r="AQ122" s="1"/>
@@ -16102,7 +16109,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN123" s="1"/>
+      <c r="AN123" s="7"/>
       <c r="AO123" s="1"/>
       <c r="AP123" s="1"/>
       <c r="AQ123" s="1"/>
@@ -16221,7 +16228,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN124" s="1"/>
+      <c r="AN124" s="7"/>
       <c r="AO124" s="1"/>
       <c r="AP124" s="1"/>
       <c r="AQ124" s="1"/>
@@ -16340,7 +16347,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN125" s="1"/>
+      <c r="AN125" s="7"/>
       <c r="AO125" s="1"/>
       <c r="AP125" s="1"/>
       <c r="AQ125" s="1"/>
@@ -16459,7 +16466,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN126" s="1"/>
+      <c r="AN126" s="7"/>
       <c r="AO126" s="1"/>
       <c r="AP126" s="1"/>
       <c r="AQ126" s="1"/>
@@ -16581,7 +16588,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN127" s="1"/>
+      <c r="AN127" s="7"/>
       <c r="AO127" s="1"/>
       <c r="AP127" s="1"/>
       <c r="AQ127" s="1"/>
@@ -16700,7 +16707,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN128" s="1"/>
+      <c r="AN128" s="7"/>
       <c r="AO128" s="1"/>
       <c r="AP128" s="1"/>
       <c r="AQ128" s="1"/>
@@ -16809,7 +16816,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN129" s="1"/>
+      <c r="AN129" s="7"/>
       <c r="AO129" s="1"/>
       <c r="AP129" s="1"/>
       <c r="AQ129" s="1"/>
@@ -16918,7 +16925,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN130" s="1"/>
+      <c r="AN130" s="7"/>
       <c r="AO130" s="1"/>
       <c r="AP130" s="1"/>
       <c r="AQ130" s="1"/>
@@ -17027,7 +17034,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AN131" s="1"/>
+      <c r="AN131" s="7"/>
       <c r="AO131" s="1"/>
       <c r="AP131" s="1"/>
       <c r="AQ131" s="1"/>
@@ -17077,7 +17084,7 @@
       <c r="AK132" s="1"/>
       <c r="AL132" s="1"/>
       <c r="AM132" s="1"/>
-      <c r="AN132" s="1"/>
+      <c r="AN132" s="7"/>
       <c r="AO132" s="1"/>
       <c r="AP132" s="1"/>
       <c r="AQ132" s="1"/>
@@ -17127,7 +17134,7 @@
       <c r="AK133" s="1"/>
       <c r="AL133" s="1"/>
       <c r="AM133" s="1"/>
-      <c r="AN133" s="1"/>
+      <c r="AN133" s="7"/>
       <c r="AO133" s="1"/>
       <c r="AP133" s="1"/>
       <c r="AQ133" s="1"/>
@@ -17177,7 +17184,7 @@
       <c r="AK134" s="1"/>
       <c r="AL134" s="1"/>
       <c r="AM134" s="1"/>
-      <c r="AN134" s="1"/>
+      <c r="AN134" s="7"/>
       <c r="AO134" s="1"/>
       <c r="AP134" s="1"/>
       <c r="AQ134" s="1"/>
@@ -17227,7 +17234,7 @@
       <c r="AK135" s="1"/>
       <c r="AL135" s="1"/>
       <c r="AM135" s="1"/>
-      <c r="AN135" s="1"/>
+      <c r="AN135" s="7"/>
       <c r="AO135" s="1"/>
       <c r="AP135" s="1"/>
       <c r="AQ135" s="1"/>
@@ -17277,7 +17284,7 @@
       <c r="AK136" s="1"/>
       <c r="AL136" s="1"/>
       <c r="AM136" s="1"/>
-      <c r="AN136" s="1"/>
+      <c r="AN136" s="7"/>
       <c r="AO136" s="1"/>
       <c r="AP136" s="1"/>
       <c r="AQ136" s="1"/>
@@ -17327,7 +17334,7 @@
       <c r="AK137" s="1"/>
       <c r="AL137" s="1"/>
       <c r="AM137" s="1"/>
-      <c r="AN137" s="1"/>
+      <c r="AN137" s="7"/>
       <c r="AO137" s="1"/>
       <c r="AP137" s="1"/>
       <c r="AQ137" s="1"/>
@@ -17377,7 +17384,7 @@
       <c r="AK138" s="1"/>
       <c r="AL138" s="1"/>
       <c r="AM138" s="1"/>
-      <c r="AN138" s="1"/>
+      <c r="AN138" s="7"/>
       <c r="AO138" s="1"/>
       <c r="AP138" s="1"/>
       <c r="AQ138" s="1"/>
@@ -17427,7 +17434,7 @@
       <c r="AK139" s="1"/>
       <c r="AL139" s="1"/>
       <c r="AM139" s="1"/>
-      <c r="AN139" s="1"/>
+      <c r="AN139" s="7"/>
       <c r="AO139" s="1"/>
       <c r="AP139" s="1"/>
       <c r="AQ139" s="1"/>
@@ -17477,7 +17484,7 @@
       <c r="AK140" s="1"/>
       <c r="AL140" s="1"/>
       <c r="AM140" s="1"/>
-      <c r="AN140" s="1"/>
+      <c r="AN140" s="7"/>
       <c r="AO140" s="1"/>
       <c r="AP140" s="1"/>
       <c r="AQ140" s="1"/>
@@ -17527,7 +17534,7 @@
       <c r="AK141" s="1"/>
       <c r="AL141" s="1"/>
       <c r="AM141" s="1"/>
-      <c r="AN141" s="1"/>
+      <c r="AN141" s="7"/>
       <c r="AO141" s="1"/>
       <c r="AP141" s="1"/>
       <c r="AQ141" s="1"/>
@@ -17577,7 +17584,7 @@
       <c r="AK142" s="1"/>
       <c r="AL142" s="1"/>
       <c r="AM142" s="1"/>
-      <c r="AN142" s="1"/>
+      <c r="AN142" s="7"/>
       <c r="AO142" s="1"/>
       <c r="AP142" s="1"/>
       <c r="AQ142" s="1"/>
@@ -17627,7 +17634,7 @@
       <c r="AK143" s="1"/>
       <c r="AL143" s="1"/>
       <c r="AM143" s="1"/>
-      <c r="AN143" s="1"/>
+      <c r="AN143" s="7"/>
       <c r="AO143" s="1"/>
       <c r="AP143" s="1"/>
       <c r="AQ143" s="1"/>
@@ -17677,7 +17684,7 @@
       <c r="AK144" s="1"/>
       <c r="AL144" s="1"/>
       <c r="AM144" s="1"/>
-      <c r="AN144" s="1"/>
+      <c r="AN144" s="7"/>
       <c r="AO144" s="1"/>
       <c r="AP144" s="1"/>
       <c r="AQ144" s="1"/>
@@ -17727,7 +17734,7 @@
       <c r="AK145" s="1"/>
       <c r="AL145" s="1"/>
       <c r="AM145" s="1"/>
-      <c r="AN145" s="1"/>
+      <c r="AN145" s="7"/>
       <c r="AO145" s="1"/>
       <c r="AP145" s="1"/>
       <c r="AQ145" s="1"/>
@@ -17777,7 +17784,7 @@
       <c r="AK146" s="1"/>
       <c r="AL146" s="1"/>
       <c r="AM146" s="1"/>
-      <c r="AN146" s="1"/>
+      <c r="AN146" s="7"/>
       <c r="AO146" s="1"/>
       <c r="AP146" s="1"/>
       <c r="AQ146" s="1"/>
@@ -17827,7 +17834,7 @@
       <c r="AK147" s="1"/>
       <c r="AL147" s="1"/>
       <c r="AM147" s="1"/>
-      <c r="AN147" s="1"/>
+      <c r="AN147" s="7"/>
       <c r="AO147" s="1"/>
       <c r="AP147" s="1"/>
       <c r="AQ147" s="1"/>
@@ -17877,7 +17884,7 @@
       <c r="AK148" s="1"/>
       <c r="AL148" s="1"/>
       <c r="AM148" s="1"/>
-      <c r="AN148" s="1"/>
+      <c r="AN148" s="7"/>
       <c r="AO148" s="1"/>
       <c r="AP148" s="1"/>
       <c r="AQ148" s="1"/>
@@ -17927,7 +17934,7 @@
       <c r="AK149" s="1"/>
       <c r="AL149" s="1"/>
       <c r="AM149" s="1"/>
-      <c r="AN149" s="1"/>
+      <c r="AN149" s="7"/>
       <c r="AO149" s="1"/>
       <c r="AP149" s="1"/>
       <c r="AQ149" s="1"/>
@@ -17977,7 +17984,7 @@
       <c r="AK150" s="1"/>
       <c r="AL150" s="1"/>
       <c r="AM150" s="1"/>
-      <c r="AN150" s="1"/>
+      <c r="AN150" s="7"/>
       <c r="AO150" s="1"/>
       <c r="AP150" s="1"/>
       <c r="AQ150" s="1"/>
@@ -18027,7 +18034,7 @@
       <c r="AK151" s="1"/>
       <c r="AL151" s="1"/>
       <c r="AM151" s="1"/>
-      <c r="AN151" s="1"/>
+      <c r="AN151" s="7"/>
       <c r="AO151" s="1"/>
       <c r="AP151" s="1"/>
       <c r="AQ151" s="1"/>
@@ -18077,7 +18084,7 @@
       <c r="AK152" s="1"/>
       <c r="AL152" s="1"/>
       <c r="AM152" s="1"/>
-      <c r="AN152" s="1"/>
+      <c r="AN152" s="7"/>
       <c r="AO152" s="1"/>
       <c r="AP152" s="1"/>
       <c r="AQ152" s="1"/>
@@ -18127,7 +18134,7 @@
       <c r="AK153" s="1"/>
       <c r="AL153" s="1"/>
       <c r="AM153" s="1"/>
-      <c r="AN153" s="1"/>
+      <c r="AN153" s="7"/>
       <c r="AO153" s="1"/>
       <c r="AP153" s="1"/>
       <c r="AQ153" s="1"/>
@@ -18177,7 +18184,7 @@
       <c r="AK154" s="1"/>
       <c r="AL154" s="1"/>
       <c r="AM154" s="1"/>
-      <c r="AN154" s="1"/>
+      <c r="AN154" s="7"/>
       <c r="AO154" s="1"/>
       <c r="AP154" s="1"/>
       <c r="AQ154" s="1"/>
@@ -18227,7 +18234,7 @@
       <c r="AK155" s="1"/>
       <c r="AL155" s="1"/>
       <c r="AM155" s="1"/>
-      <c r="AN155" s="1"/>
+      <c r="AN155" s="7"/>
       <c r="AO155" s="1"/>
       <c r="AP155" s="1"/>
       <c r="AQ155" s="1"/>
@@ -18277,7 +18284,7 @@
       <c r="AK156" s="1"/>
       <c r="AL156" s="1"/>
       <c r="AM156" s="1"/>
-      <c r="AN156" s="1"/>
+      <c r="AN156" s="7"/>
       <c r="AO156" s="1"/>
       <c r="AP156" s="1"/>
       <c r="AQ156" s="1"/>
@@ -18327,7 +18334,7 @@
       <c r="AK157" s="1"/>
       <c r="AL157" s="1"/>
       <c r="AM157" s="1"/>
-      <c r="AN157" s="1"/>
+      <c r="AN157" s="7"/>
       <c r="AO157" s="1"/>
       <c r="AP157" s="1"/>
       <c r="AQ157" s="1"/>
@@ -18377,7 +18384,7 @@
       <c r="AK158" s="1"/>
       <c r="AL158" s="1"/>
       <c r="AM158" s="1"/>
-      <c r="AN158" s="1"/>
+      <c r="AN158" s="7"/>
       <c r="AO158" s="1"/>
       <c r="AP158" s="1"/>
       <c r="AQ158" s="1"/>
@@ -18427,7 +18434,7 @@
       <c r="AK159" s="1"/>
       <c r="AL159" s="1"/>
       <c r="AM159" s="1"/>
-      <c r="AN159" s="1"/>
+      <c r="AN159" s="7"/>
       <c r="AO159" s="1"/>
       <c r="AP159" s="1"/>
       <c r="AQ159" s="1"/>
@@ -18477,7 +18484,7 @@
       <c r="AK160" s="1"/>
       <c r="AL160" s="1"/>
       <c r="AM160" s="1"/>
-      <c r="AN160" s="1"/>
+      <c r="AN160" s="7"/>
       <c r="AO160" s="1"/>
       <c r="AP160" s="1"/>
       <c r="AQ160" s="1"/>
@@ -18527,7 +18534,7 @@
       <c r="AK161" s="1"/>
       <c r="AL161" s="1"/>
       <c r="AM161" s="1"/>
-      <c r="AN161" s="1"/>
+      <c r="AN161" s="7"/>
       <c r="AO161" s="1"/>
       <c r="AP161" s="1"/>
       <c r="AQ161" s="1"/>
@@ -18577,7 +18584,7 @@
       <c r="AK162" s="1"/>
       <c r="AL162" s="1"/>
       <c r="AM162" s="1"/>
-      <c r="AN162" s="1"/>
+      <c r="AN162" s="7"/>
       <c r="AO162" s="1"/>
       <c r="AP162" s="1"/>
       <c r="AQ162" s="1"/>
@@ -18627,7 +18634,7 @@
       <c r="AK163" s="1"/>
       <c r="AL163" s="1"/>
       <c r="AM163" s="1"/>
-      <c r="AN163" s="1"/>
+      <c r="AN163" s="7"/>
       <c r="AO163" s="1"/>
       <c r="AP163" s="1"/>
       <c r="AQ163" s="1"/>
@@ -18677,7 +18684,7 @@
       <c r="AK164" s="1"/>
       <c r="AL164" s="1"/>
       <c r="AM164" s="1"/>
-      <c r="AN164" s="1"/>
+      <c r="AN164" s="7"/>
       <c r="AO164" s="1"/>
       <c r="AP164" s="1"/>
       <c r="AQ164" s="1"/>
@@ -18727,7 +18734,7 @@
       <c r="AK165" s="1"/>
       <c r="AL165" s="1"/>
       <c r="AM165" s="1"/>
-      <c r="AN165" s="1"/>
+      <c r="AN165" s="7"/>
       <c r="AO165" s="1"/>
       <c r="AP165" s="1"/>
       <c r="AQ165" s="1"/>
@@ -18777,7 +18784,7 @@
       <c r="AK166" s="1"/>
       <c r="AL166" s="1"/>
       <c r="AM166" s="1"/>
-      <c r="AN166" s="1"/>
+      <c r="AN166" s="7"/>
       <c r="AO166" s="1"/>
       <c r="AP166" s="1"/>
       <c r="AQ166" s="1"/>
@@ -18827,7 +18834,7 @@
       <c r="AK167" s="1"/>
       <c r="AL167" s="1"/>
       <c r="AM167" s="1"/>
-      <c r="AN167" s="1"/>
+      <c r="AN167" s="7"/>
       <c r="AO167" s="1"/>
       <c r="AP167" s="1"/>
       <c r="AQ167" s="1"/>
@@ -18877,7 +18884,7 @@
       <c r="AK168" s="1"/>
       <c r="AL168" s="1"/>
       <c r="AM168" s="1"/>
-      <c r="AN168" s="1"/>
+      <c r="AN168" s="7"/>
       <c r="AO168" s="1"/>
       <c r="AP168" s="1"/>
       <c r="AQ168" s="1"/>
@@ -18927,7 +18934,7 @@
       <c r="AK169" s="1"/>
       <c r="AL169" s="1"/>
       <c r="AM169" s="1"/>
-      <c r="AN169" s="1"/>
+      <c r="AN169" s="7"/>
       <c r="AO169" s="1"/>
       <c r="AP169" s="1"/>
       <c r="AQ169" s="1"/>
@@ -18977,7 +18984,7 @@
       <c r="AK170" s="1"/>
       <c r="AL170" s="1"/>
       <c r="AM170" s="1"/>
-      <c r="AN170" s="1"/>
+      <c r="AN170" s="7"/>
       <c r="AO170" s="1"/>
       <c r="AP170" s="1"/>
       <c r="AQ170" s="1"/>
@@ -19027,7 +19034,7 @@
       <c r="AK171" s="1"/>
       <c r="AL171" s="1"/>
       <c r="AM171" s="1"/>
-      <c r="AN171" s="1"/>
+      <c r="AN171" s="7"/>
       <c r="AO171" s="1"/>
       <c r="AP171" s="1"/>
       <c r="AQ171" s="1"/>
@@ -19077,7 +19084,7 @@
       <c r="AK172" s="1"/>
       <c r="AL172" s="1"/>
       <c r="AM172" s="1"/>
-      <c r="AN172" s="1"/>
+      <c r="AN172" s="7"/>
       <c r="AO172" s="1"/>
       <c r="AP172" s="1"/>
       <c r="AQ172" s="1"/>
@@ -19127,7 +19134,7 @@
       <c r="AK173" s="1"/>
       <c r="AL173" s="1"/>
       <c r="AM173" s="1"/>
-      <c r="AN173" s="1"/>
+      <c r="AN173" s="7"/>
       <c r="AO173" s="1"/>
       <c r="AP173" s="1"/>
       <c r="AQ173" s="1"/>
@@ -19177,7 +19184,7 @@
       <c r="AK174" s="1"/>
       <c r="AL174" s="1"/>
       <c r="AM174" s="1"/>
-      <c r="AN174" s="1"/>
+      <c r="AN174" s="7"/>
       <c r="AO174" s="1"/>
       <c r="AP174" s="1"/>
       <c r="AQ174" s="1"/>
@@ -19227,7 +19234,7 @@
       <c r="AK175" s="1"/>
       <c r="AL175" s="1"/>
       <c r="AM175" s="1"/>
-      <c r="AN175" s="1"/>
+      <c r="AN175" s="7"/>
       <c r="AO175" s="1"/>
       <c r="AP175" s="1"/>
       <c r="AQ175" s="1"/>
@@ -19277,7 +19284,7 @@
       <c r="AK176" s="1"/>
       <c r="AL176" s="1"/>
       <c r="AM176" s="1"/>
-      <c r="AN176" s="1"/>
+      <c r="AN176" s="7"/>
       <c r="AO176" s="1"/>
       <c r="AP176" s="1"/>
       <c r="AQ176" s="1"/>
@@ -19327,7 +19334,7 @@
       <c r="AK177" s="1"/>
       <c r="AL177" s="1"/>
       <c r="AM177" s="1"/>
-      <c r="AN177" s="1"/>
+      <c r="AN177" s="7"/>
       <c r="AO177" s="1"/>
       <c r="AP177" s="1"/>
       <c r="AQ177" s="1"/>
@@ -19377,7 +19384,7 @@
       <c r="AK178" s="1"/>
       <c r="AL178" s="1"/>
       <c r="AM178" s="1"/>
-      <c r="AN178" s="1"/>
+      <c r="AN178" s="7"/>
       <c r="AO178" s="1"/>
       <c r="AP178" s="1"/>
       <c r="AQ178" s="1"/>
@@ -19427,7 +19434,7 @@
       <c r="AK179" s="1"/>
       <c r="AL179" s="1"/>
       <c r="AM179" s="1"/>
-      <c r="AN179" s="1"/>
+      <c r="AN179" s="7"/>
       <c r="AO179" s="1"/>
       <c r="AP179" s="1"/>
       <c r="AQ179" s="1"/>
@@ -19477,7 +19484,7 @@
       <c r="AK180" s="1"/>
       <c r="AL180" s="1"/>
       <c r="AM180" s="1"/>
-      <c r="AN180" s="1"/>
+      <c r="AN180" s="7"/>
       <c r="AO180" s="1"/>
       <c r="AP180" s="1"/>
       <c r="AQ180" s="1"/>
@@ -19527,7 +19534,7 @@
       <c r="AK181" s="1"/>
       <c r="AL181" s="1"/>
       <c r="AM181" s="1"/>
-      <c r="AN181" s="1"/>
+      <c r="AN181" s="7"/>
       <c r="AO181" s="1"/>
       <c r="AP181" s="1"/>
       <c r="AQ181" s="1"/>
@@ -19577,7 +19584,7 @@
       <c r="AK182" s="1"/>
       <c r="AL182" s="1"/>
       <c r="AM182" s="1"/>
-      <c r="AN182" s="1"/>
+      <c r="AN182" s="7"/>
       <c r="AO182" s="1"/>
       <c r="AP182" s="1"/>
       <c r="AQ182" s="1"/>
@@ -19627,7 +19634,7 @@
       <c r="AK183" s="1"/>
       <c r="AL183" s="1"/>
       <c r="AM183" s="1"/>
-      <c r="AN183" s="1"/>
+      <c r="AN183" s="7"/>
       <c r="AO183" s="1"/>
       <c r="AP183" s="1"/>
       <c r="AQ183" s="1"/>
@@ -19677,7 +19684,7 @@
       <c r="AK184" s="1"/>
       <c r="AL184" s="1"/>
       <c r="AM184" s="1"/>
-      <c r="AN184" s="1"/>
+      <c r="AN184" s="7"/>
       <c r="AO184" s="1"/>
       <c r="AP184" s="1"/>
       <c r="AQ184" s="1"/>
@@ -19727,7 +19734,7 @@
       <c r="AK185" s="1"/>
       <c r="AL185" s="1"/>
       <c r="AM185" s="1"/>
-      <c r="AN185" s="1"/>
+      <c r="AN185" s="7"/>
       <c r="AO185" s="1"/>
       <c r="AP185" s="1"/>
       <c r="AQ185" s="1"/>
@@ -19777,7 +19784,7 @@
       <c r="AK186" s="1"/>
       <c r="AL186" s="1"/>
       <c r="AM186" s="1"/>
-      <c r="AN186" s="1"/>
+      <c r="AN186" s="7"/>
       <c r="AO186" s="1"/>
       <c r="AP186" s="1"/>
       <c r="AQ186" s="1"/>
@@ -19827,7 +19834,7 @@
       <c r="AK187" s="1"/>
       <c r="AL187" s="1"/>
       <c r="AM187" s="1"/>
-      <c r="AN187" s="1"/>
+      <c r="AN187" s="7"/>
       <c r="AO187" s="1"/>
       <c r="AP187" s="1"/>
       <c r="AQ187" s="1"/>
@@ -19877,7 +19884,7 @@
       <c r="AK188" s="1"/>
       <c r="AL188" s="1"/>
       <c r="AM188" s="1"/>
-      <c r="AN188" s="1"/>
+      <c r="AN188" s="7"/>
       <c r="AO188" s="1"/>
       <c r="AP188" s="1"/>
       <c r="AQ188" s="1"/>
@@ -19927,7 +19934,7 @@
       <c r="AK189" s="1"/>
       <c r="AL189" s="1"/>
       <c r="AM189" s="1"/>
-      <c r="AN189" s="1"/>
+      <c r="AN189" s="7"/>
       <c r="AO189" s="1"/>
       <c r="AP189" s="1"/>
       <c r="AQ189" s="1"/>
@@ -19977,7 +19984,7 @@
       <c r="AK190" s="1"/>
       <c r="AL190" s="1"/>
       <c r="AM190" s="1"/>
-      <c r="AN190" s="1"/>
+      <c r="AN190" s="7"/>
       <c r="AO190" s="1"/>
       <c r="AP190" s="1"/>
       <c r="AQ190" s="1"/>
@@ -20027,7 +20034,7 @@
       <c r="AK191" s="1"/>
       <c r="AL191" s="1"/>
       <c r="AM191" s="1"/>
-      <c r="AN191" s="1"/>
+      <c r="AN191" s="7"/>
       <c r="AO191" s="1"/>
       <c r="AP191" s="1"/>
       <c r="AQ191" s="1"/>
@@ -20077,7 +20084,7 @@
       <c r="AK192" s="1"/>
       <c r="AL192" s="1"/>
       <c r="AM192" s="1"/>
-      <c r="AN192" s="1"/>
+      <c r="AN192" s="7"/>
       <c r="AO192" s="1"/>
       <c r="AP192" s="1"/>
       <c r="AQ192" s="1"/>
@@ -20127,7 +20134,7 @@
       <c r="AK193" s="1"/>
       <c r="AL193" s="1"/>
       <c r="AM193" s="1"/>
-      <c r="AN193" s="1"/>
+      <c r="AN193" s="7"/>
       <c r="AO193" s="1"/>
       <c r="AP193" s="1"/>
       <c r="AQ193" s="1"/>
@@ -20177,7 +20184,7 @@
       <c r="AK194" s="1"/>
       <c r="AL194" s="1"/>
       <c r="AM194" s="1"/>
-      <c r="AN194" s="1"/>
+      <c r="AN194" s="7"/>
       <c r="AO194" s="1"/>
       <c r="AP194" s="1"/>
       <c r="AQ194" s="1"/>
@@ -20227,7 +20234,7 @@
       <c r="AK195" s="1"/>
       <c r="AL195" s="1"/>
       <c r="AM195" s="1"/>
-      <c r="AN195" s="1"/>
+      <c r="AN195" s="7"/>
       <c r="AO195" s="1"/>
       <c r="AP195" s="1"/>
       <c r="AQ195" s="1"/>
@@ -20277,7 +20284,7 @@
       <c r="AK196" s="1"/>
       <c r="AL196" s="1"/>
       <c r="AM196" s="1"/>
-      <c r="AN196" s="1"/>
+      <c r="AN196" s="7"/>
       <c r="AO196" s="1"/>
       <c r="AP196" s="1"/>
       <c r="AQ196" s="1"/>
@@ -20327,7 +20334,7 @@
       <c r="AK197" s="1"/>
       <c r="AL197" s="1"/>
       <c r="AM197" s="1"/>
-      <c r="AN197" s="1"/>
+      <c r="AN197" s="7"/>
       <c r="AO197" s="1"/>
       <c r="AP197" s="1"/>
       <c r="AQ197" s="1"/>
@@ -20377,7 +20384,7 @@
       <c r="AK198" s="1"/>
       <c r="AL198" s="1"/>
       <c r="AM198" s="1"/>
-      <c r="AN198" s="1"/>
+      <c r="AN198" s="7"/>
       <c r="AO198" s="1"/>
       <c r="AP198" s="1"/>
       <c r="AQ198" s="1"/>
@@ -20427,7 +20434,7 @@
       <c r="AK199" s="1"/>
       <c r="AL199" s="1"/>
       <c r="AM199" s="1"/>
-      <c r="AN199" s="1"/>
+      <c r="AN199" s="7"/>
       <c r="AO199" s="1"/>
       <c r="AP199" s="1"/>
       <c r="AQ199" s="1"/>
@@ -20477,7 +20484,7 @@
       <c r="AK200" s="1"/>
       <c r="AL200" s="1"/>
       <c r="AM200" s="1"/>
-      <c r="AN200" s="1"/>
+      <c r="AN200" s="7"/>
       <c r="AO200" s="1"/>
       <c r="AP200" s="1"/>
       <c r="AQ200" s="1"/>
@@ -20527,7 +20534,7 @@
       <c r="AK201" s="1"/>
       <c r="AL201" s="1"/>
       <c r="AM201" s="1"/>
-      <c r="AN201" s="1"/>
+      <c r="AN201" s="7"/>
       <c r="AO201" s="1"/>
       <c r="AP201" s="1"/>
       <c r="AQ201" s="1"/>
@@ -20577,7 +20584,7 @@
       <c r="AK202" s="1"/>
       <c r="AL202" s="1"/>
       <c r="AM202" s="1"/>
-      <c r="AN202" s="1"/>
+      <c r="AN202" s="7"/>
       <c r="AO202" s="1"/>
       <c r="AP202" s="1"/>
       <c r="AQ202" s="1"/>
@@ -20627,7 +20634,7 @@
       <c r="AK203" s="1"/>
       <c r="AL203" s="1"/>
       <c r="AM203" s="1"/>
-      <c r="AN203" s="1"/>
+      <c r="AN203" s="7"/>
       <c r="AO203" s="1"/>
       <c r="AP203" s="1"/>
       <c r="AQ203" s="1"/>
@@ -20677,7 +20684,7 @@
       <c r="AK204" s="1"/>
       <c r="AL204" s="1"/>
       <c r="AM204" s="1"/>
-      <c r="AN204" s="1"/>
+      <c r="AN204" s="7"/>
       <c r="AO204" s="1"/>
       <c r="AP204" s="1"/>
       <c r="AQ204" s="1"/>
@@ -20727,7 +20734,7 @@
       <c r="AK205" s="1"/>
       <c r="AL205" s="1"/>
       <c r="AM205" s="1"/>
-      <c r="AN205" s="1"/>
+      <c r="AN205" s="7"/>
       <c r="AO205" s="1"/>
       <c r="AP205" s="1"/>
       <c r="AQ205" s="1"/>
@@ -20777,7 +20784,7 @@
       <c r="AK206" s="1"/>
       <c r="AL206" s="1"/>
       <c r="AM206" s="1"/>
-      <c r="AN206" s="1"/>
+      <c r="AN206" s="7"/>
       <c r="AO206" s="1"/>
       <c r="AP206" s="1"/>
       <c r="AQ206" s="1"/>
@@ -20827,7 +20834,7 @@
       <c r="AK207" s="1"/>
       <c r="AL207" s="1"/>
       <c r="AM207" s="1"/>
-      <c r="AN207" s="1"/>
+      <c r="AN207" s="7"/>
       <c r="AO207" s="1"/>
       <c r="AP207" s="1"/>
       <c r="AQ207" s="1"/>
@@ -20877,7 +20884,7 @@
       <c r="AK208" s="1"/>
       <c r="AL208" s="1"/>
       <c r="AM208" s="1"/>
-      <c r="AN208" s="1"/>
+      <c r="AN208" s="7"/>
       <c r="AO208" s="1"/>
       <c r="AP208" s="1"/>
       <c r="AQ208" s="1"/>
@@ -20927,7 +20934,7 @@
       <c r="AK209" s="1"/>
       <c r="AL209" s="1"/>
       <c r="AM209" s="1"/>
-      <c r="AN209" s="1"/>
+      <c r="AN209" s="7"/>
       <c r="AO209" s="1"/>
       <c r="AP209" s="1"/>
       <c r="AQ209" s="1"/>
@@ -20977,7 +20984,7 @@
       <c r="AK210" s="1"/>
       <c r="AL210" s="1"/>
       <c r="AM210" s="1"/>
-      <c r="AN210" s="1"/>
+      <c r="AN210" s="7"/>
       <c r="AO210" s="1"/>
       <c r="AP210" s="1"/>
       <c r="AQ210" s="1"/>
@@ -21027,7 +21034,7 @@
       <c r="AK211" s="1"/>
       <c r="AL211" s="1"/>
       <c r="AM211" s="1"/>
-      <c r="AN211" s="1"/>
+      <c r="AN211" s="7"/>
       <c r="AO211" s="1"/>
       <c r="AP211" s="1"/>
       <c r="AQ211" s="1"/>
@@ -21077,7 +21084,7 @@
       <c r="AK212" s="1"/>
       <c r="AL212" s="1"/>
       <c r="AM212" s="1"/>
-      <c r="AN212" s="1"/>
+      <c r="AN212" s="7"/>
       <c r="AO212" s="1"/>
       <c r="AP212" s="1"/>
       <c r="AQ212" s="1"/>
@@ -21127,7 +21134,7 @@
       <c r="AK213" s="1"/>
       <c r="AL213" s="1"/>
       <c r="AM213" s="1"/>
-      <c r="AN213" s="1"/>
+      <c r="AN213" s="7"/>
       <c r="AO213" s="1"/>
       <c r="AP213" s="1"/>
       <c r="AQ213" s="1"/>
@@ -21177,7 +21184,7 @@
       <c r="AK214" s="1"/>
       <c r="AL214" s="1"/>
       <c r="AM214" s="1"/>
-      <c r="AN214" s="1"/>
+      <c r="AN214" s="7"/>
       <c r="AO214" s="1"/>
       <c r="AP214" s="1"/>
       <c r="AQ214" s="1"/>
@@ -21227,7 +21234,7 @@
       <c r="AK215" s="1"/>
       <c r="AL215" s="1"/>
       <c r="AM215" s="1"/>
-      <c r="AN215" s="1"/>
+      <c r="AN215" s="7"/>
       <c r="AO215" s="1"/>
       <c r="AP215" s="1"/>
       <c r="AQ215" s="1"/>
@@ -21277,7 +21284,7 @@
       <c r="AK216" s="1"/>
       <c r="AL216" s="1"/>
       <c r="AM216" s="1"/>
-      <c r="AN216" s="1"/>
+      <c r="AN216" s="7"/>
       <c r="AO216" s="1"/>
       <c r="AP216" s="1"/>
       <c r="AQ216" s="1"/>
@@ -21327,7 +21334,7 @@
       <c r="AK217" s="1"/>
       <c r="AL217" s="1"/>
       <c r="AM217" s="1"/>
-      <c r="AN217" s="1"/>
+      <c r="AN217" s="7"/>
       <c r="AO217" s="1"/>
       <c r="AP217" s="1"/>
       <c r="AQ217" s="1"/>
@@ -21377,7 +21384,7 @@
       <c r="AK218" s="1"/>
       <c r="AL218" s="1"/>
       <c r="AM218" s="1"/>
-      <c r="AN218" s="1"/>
+      <c r="AN218" s="7"/>
       <c r="AO218" s="1"/>
       <c r="AP218" s="1"/>
       <c r="AQ218" s="1"/>
@@ -21427,7 +21434,7 @@
       <c r="AK219" s="1"/>
       <c r="AL219" s="1"/>
       <c r="AM219" s="1"/>
-      <c r="AN219" s="1"/>
+      <c r="AN219" s="7"/>
       <c r="AO219" s="1"/>
       <c r="AP219" s="1"/>
       <c r="AQ219" s="1"/>
@@ -21477,7 +21484,7 @@
       <c r="AK220" s="1"/>
       <c r="AL220" s="1"/>
       <c r="AM220" s="1"/>
-      <c r="AN220" s="1"/>
+      <c r="AN220" s="7"/>
       <c r="AO220" s="1"/>
       <c r="AP220" s="1"/>
       <c r="AQ220" s="1"/>
@@ -21527,7 +21534,7 @@
       <c r="AK221" s="1"/>
       <c r="AL221" s="1"/>
       <c r="AM221" s="1"/>
-      <c r="AN221" s="1"/>
+      <c r="AN221" s="7"/>
       <c r="AO221" s="1"/>
       <c r="AP221" s="1"/>
       <c r="AQ221" s="1"/>
@@ -21577,7 +21584,7 @@
       <c r="AK222" s="1"/>
       <c r="AL222" s="1"/>
       <c r="AM222" s="1"/>
-      <c r="AN222" s="1"/>
+      <c r="AN222" s="7"/>
       <c r="AO222" s="1"/>
       <c r="AP222" s="1"/>
       <c r="AQ222" s="1"/>
@@ -21627,7 +21634,7 @@
       <c r="AK223" s="1"/>
       <c r="AL223" s="1"/>
       <c r="AM223" s="1"/>
-      <c r="AN223" s="1"/>
+      <c r="AN223" s="7"/>
       <c r="AO223" s="1"/>
       <c r="AP223" s="1"/>
       <c r="AQ223" s="1"/>
@@ -21677,7 +21684,7 @@
       <c r="AK224" s="1"/>
       <c r="AL224" s="1"/>
       <c r="AM224" s="1"/>
-      <c r="AN224" s="1"/>
+      <c r="AN224" s="7"/>
       <c r="AO224" s="1"/>
       <c r="AP224" s="1"/>
       <c r="AQ224" s="1"/>
@@ -21727,7 +21734,7 @@
       <c r="AK225" s="1"/>
       <c r="AL225" s="1"/>
       <c r="AM225" s="1"/>
-      <c r="AN225" s="1"/>
+      <c r="AN225" s="7"/>
       <c r="AO225" s="1"/>
       <c r="AP225" s="1"/>
       <c r="AQ225" s="1"/>
@@ -21777,7 +21784,7 @@
       <c r="AK226" s="1"/>
       <c r="AL226" s="1"/>
       <c r="AM226" s="1"/>
-      <c r="AN226" s="1"/>
+      <c r="AN226" s="7"/>
       <c r="AO226" s="1"/>
       <c r="AP226" s="1"/>
       <c r="AQ226" s="1"/>
@@ -21827,7 +21834,7 @@
       <c r="AK227" s="1"/>
       <c r="AL227" s="1"/>
       <c r="AM227" s="1"/>
-      <c r="AN227" s="1"/>
+      <c r="AN227" s="7"/>
       <c r="AO227" s="1"/>
       <c r="AP227" s="1"/>
       <c r="AQ227" s="1"/>
@@ -21877,7 +21884,7 @@
       <c r="AK228" s="1"/>
       <c r="AL228" s="1"/>
       <c r="AM228" s="1"/>
-      <c r="AN228" s="1"/>
+      <c r="AN228" s="7"/>
       <c r="AO228" s="1"/>
       <c r="AP228" s="1"/>
       <c r="AQ228" s="1"/>
@@ -21927,7 +21934,7 @@
       <c r="AK229" s="1"/>
       <c r="AL229" s="1"/>
       <c r="AM229" s="1"/>
-      <c r="AN229" s="1"/>
+      <c r="AN229" s="7"/>
       <c r="AO229" s="1"/>
       <c r="AP229" s="1"/>
       <c r="AQ229" s="1"/>
@@ -21977,7 +21984,7 @@
       <c r="AK230" s="1"/>
       <c r="AL230" s="1"/>
       <c r="AM230" s="1"/>
-      <c r="AN230" s="1"/>
+      <c r="AN230" s="7"/>
       <c r="AO230" s="1"/>
       <c r="AP230" s="1"/>
       <c r="AQ230" s="1"/>
@@ -22027,7 +22034,7 @@
       <c r="AK231" s="1"/>
       <c r="AL231" s="1"/>
       <c r="AM231" s="1"/>
-      <c r="AN231" s="1"/>
+      <c r="AN231" s="7"/>
       <c r="AO231" s="1"/>
       <c r="AP231" s="1"/>
       <c r="AQ231" s="1"/>
@@ -22077,7 +22084,7 @@
       <c r="AK232" s="1"/>
       <c r="AL232" s="1"/>
       <c r="AM232" s="1"/>
-      <c r="AN232" s="1"/>
+      <c r="AN232" s="7"/>
       <c r="AO232" s="1"/>
       <c r="AP232" s="1"/>
       <c r="AQ232" s="1"/>
@@ -22127,7 +22134,7 @@
       <c r="AK233" s="1"/>
       <c r="AL233" s="1"/>
       <c r="AM233" s="1"/>
-      <c r="AN233" s="1"/>
+      <c r="AN233" s="7"/>
       <c r="AO233" s="1"/>
       <c r="AP233" s="1"/>
       <c r="AQ233" s="1"/>
@@ -22177,7 +22184,7 @@
       <c r="AK234" s="1"/>
       <c r="AL234" s="1"/>
       <c r="AM234" s="1"/>
-      <c r="AN234" s="1"/>
+      <c r="AN234" s="7"/>
       <c r="AO234" s="1"/>
       <c r="AP234" s="1"/>
       <c r="AQ234" s="1"/>
@@ -22227,7 +22234,7 @@
       <c r="AK235" s="1"/>
       <c r="AL235" s="1"/>
       <c r="AM235" s="1"/>
-      <c r="AN235" s="1"/>
+      <c r="AN235" s="7"/>
       <c r="AO235" s="1"/>
       <c r="AP235" s="1"/>
       <c r="AQ235" s="1"/>
@@ -22277,7 +22284,7 @@
       <c r="AK236" s="1"/>
       <c r="AL236" s="1"/>
       <c r="AM236" s="1"/>
-      <c r="AN236" s="1"/>
+      <c r="AN236" s="7"/>
       <c r="AO236" s="1"/>
       <c r="AP236" s="1"/>
       <c r="AQ236" s="1"/>
@@ -22327,7 +22334,7 @@
       <c r="AK237" s="1"/>
       <c r="AL237" s="1"/>
       <c r="AM237" s="1"/>
-      <c r="AN237" s="1"/>
+      <c r="AN237" s="7"/>
       <c r="AO237" s="1"/>
       <c r="AP237" s="1"/>
       <c r="AQ237" s="1"/>
@@ -22377,7 +22384,7 @@
       <c r="AK238" s="1"/>
       <c r="AL238" s="1"/>
       <c r="AM238" s="1"/>
-      <c r="AN238" s="1"/>
+      <c r="AN238" s="7"/>
       <c r="AO238" s="1"/>
       <c r="AP238" s="1"/>
       <c r="AQ238" s="1"/>
@@ -22427,7 +22434,7 @@
       <c r="AK239" s="1"/>
       <c r="AL239" s="1"/>
       <c r="AM239" s="1"/>
-      <c r="AN239" s="1"/>
+      <c r="AN239" s="7"/>
       <c r="AO239" s="1"/>
       <c r="AP239" s="1"/>
       <c r="AQ239" s="1"/>
@@ -22477,7 +22484,7 @@
       <c r="AK240" s="1"/>
       <c r="AL240" s="1"/>
       <c r="AM240" s="1"/>
-      <c r="AN240" s="1"/>
+      <c r="AN240" s="7"/>
       <c r="AO240" s="1"/>
       <c r="AP240" s="1"/>
       <c r="AQ240" s="1"/>
@@ -22527,7 +22534,7 @@
       <c r="AK241" s="1"/>
       <c r="AL241" s="1"/>
       <c r="AM241" s="1"/>
-      <c r="AN241" s="1"/>
+      <c r="AN241" s="7"/>
       <c r="AO241" s="1"/>
       <c r="AP241" s="1"/>
       <c r="AQ241" s="1"/>
@@ -22577,7 +22584,7 @@
       <c r="AK242" s="1"/>
       <c r="AL242" s="1"/>
       <c r="AM242" s="1"/>
-      <c r="AN242" s="1"/>
+      <c r="AN242" s="7"/>
       <c r="AO242" s="1"/>
       <c r="AP242" s="1"/>
       <c r="AQ242" s="1"/>
@@ -22627,7 +22634,7 @@
       <c r="AK243" s="1"/>
       <c r="AL243" s="1"/>
       <c r="AM243" s="1"/>
-      <c r="AN243" s="1"/>
+      <c r="AN243" s="7"/>
       <c r="AO243" s="1"/>
       <c r="AP243" s="1"/>
       <c r="AQ243" s="1"/>
@@ -22677,7 +22684,7 @@
       <c r="AK244" s="1"/>
       <c r="AL244" s="1"/>
       <c r="AM244" s="1"/>
-      <c r="AN244" s="1"/>
+      <c r="AN244" s="7"/>
       <c r="AO244" s="1"/>
       <c r="AP244" s="1"/>
       <c r="AQ244" s="1"/>
@@ -22727,7 +22734,7 @@
       <c r="AK245" s="1"/>
       <c r="AL245" s="1"/>
       <c r="AM245" s="1"/>
-      <c r="AN245" s="1"/>
+      <c r="AN245" s="7"/>
       <c r="AO245" s="1"/>
       <c r="AP245" s="1"/>
       <c r="AQ245" s="1"/>
@@ -22777,7 +22784,7 @@
       <c r="AK246" s="1"/>
       <c r="AL246" s="1"/>
       <c r="AM246" s="1"/>
-      <c r="AN246" s="1"/>
+      <c r="AN246" s="7"/>
       <c r="AO246" s="1"/>
       <c r="AP246" s="1"/>
       <c r="AQ246" s="1"/>
@@ -22827,7 +22834,7 @@
       <c r="AK247" s="1"/>
       <c r="AL247" s="1"/>
       <c r="AM247" s="1"/>
-      <c r="AN247" s="1"/>
+      <c r="AN247" s="7"/>
       <c r="AO247" s="1"/>
       <c r="AP247" s="1"/>
       <c r="AQ247" s="1"/>
@@ -22877,7 +22884,7 @@
       <c r="AK248" s="1"/>
       <c r="AL248" s="1"/>
       <c r="AM248" s="1"/>
-      <c r="AN248" s="1"/>
+      <c r="AN248" s="7"/>
       <c r="AO248" s="1"/>
       <c r="AP248" s="1"/>
       <c r="AQ248" s="1"/>
@@ -22927,7 +22934,7 @@
       <c r="AK249" s="1"/>
       <c r="AL249" s="1"/>
       <c r="AM249" s="1"/>
-      <c r="AN249" s="1"/>
+      <c r="AN249" s="7"/>
       <c r="AO249" s="1"/>
       <c r="AP249" s="1"/>
       <c r="AQ249" s="1"/>
@@ -22977,7 +22984,7 @@
       <c r="AK250" s="1"/>
       <c r="AL250" s="1"/>
       <c r="AM250" s="1"/>
-      <c r="AN250" s="1"/>
+      <c r="AN250" s="7"/>
       <c r="AO250" s="1"/>
       <c r="AP250" s="1"/>
       <c r="AQ250" s="1"/>
@@ -23027,7 +23034,7 @@
       <c r="AK251" s="1"/>
       <c r="AL251" s="1"/>
       <c r="AM251" s="1"/>
-      <c r="AN251" s="1"/>
+      <c r="AN251" s="7"/>
       <c r="AO251" s="1"/>
       <c r="AP251" s="1"/>
       <c r="AQ251" s="1"/>
@@ -23077,7 +23084,7 @@
       <c r="AK252" s="1"/>
       <c r="AL252" s="1"/>
       <c r="AM252" s="1"/>
-      <c r="AN252" s="1"/>
+      <c r="AN252" s="7"/>
       <c r="AO252" s="1"/>
       <c r="AP252" s="1"/>
       <c r="AQ252" s="1"/>
@@ -23127,7 +23134,7 @@
       <c r="AK253" s="1"/>
       <c r="AL253" s="1"/>
       <c r="AM253" s="1"/>
-      <c r="AN253" s="1"/>
+      <c r="AN253" s="7"/>
       <c r="AO253" s="1"/>
       <c r="AP253" s="1"/>
       <c r="AQ253" s="1"/>
@@ -23177,7 +23184,7 @@
       <c r="AK254" s="1"/>
       <c r="AL254" s="1"/>
       <c r="AM254" s="1"/>
-      <c r="AN254" s="1"/>
+      <c r="AN254" s="7"/>
       <c r="AO254" s="1"/>
       <c r="AP254" s="1"/>
       <c r="AQ254" s="1"/>
@@ -23227,7 +23234,7 @@
       <c r="AK255" s="1"/>
       <c r="AL255" s="1"/>
       <c r="AM255" s="1"/>
-      <c r="AN255" s="1"/>
+      <c r="AN255" s="7"/>
       <c r="AO255" s="1"/>
       <c r="AP255" s="1"/>
       <c r="AQ255" s="1"/>
@@ -23277,7 +23284,7 @@
       <c r="AK256" s="1"/>
       <c r="AL256" s="1"/>
       <c r="AM256" s="1"/>
-      <c r="AN256" s="1"/>
+      <c r="AN256" s="7"/>
       <c r="AO256" s="1"/>
       <c r="AP256" s="1"/>
       <c r="AQ256" s="1"/>
@@ -23327,7 +23334,7 @@
       <c r="AK257" s="1"/>
       <c r="AL257" s="1"/>
       <c r="AM257" s="1"/>
-      <c r="AN257" s="1"/>
+      <c r="AN257" s="7"/>
       <c r="AO257" s="1"/>
       <c r="AP257" s="1"/>
       <c r="AQ257" s="1"/>
@@ -23377,7 +23384,7 @@
       <c r="AK258" s="1"/>
       <c r="AL258" s="1"/>
       <c r="AM258" s="1"/>
-      <c r="AN258" s="1"/>
+      <c r="AN258" s="7"/>
       <c r="AO258" s="1"/>
       <c r="AP258" s="1"/>
       <c r="AQ258" s="1"/>
@@ -23427,7 +23434,7 @@
       <c r="AK259" s="1"/>
       <c r="AL259" s="1"/>
       <c r="AM259" s="1"/>
-      <c r="AN259" s="1"/>
+      <c r="AN259" s="7"/>
       <c r="AO259" s="1"/>
       <c r="AP259" s="1"/>
       <c r="AQ259" s="1"/>
@@ -23477,7 +23484,7 @@
       <c r="AK260" s="1"/>
       <c r="AL260" s="1"/>
       <c r="AM260" s="1"/>
-      <c r="AN260" s="1"/>
+      <c r="AN260" s="7"/>
       <c r="AO260" s="1"/>
       <c r="AP260" s="1"/>
       <c r="AQ260" s="1"/>
@@ -23527,7 +23534,7 @@
       <c r="AK261" s="1"/>
       <c r="AL261" s="1"/>
       <c r="AM261" s="1"/>
-      <c r="AN261" s="1"/>
+      <c r="AN261" s="7"/>
       <c r="AO261" s="1"/>
       <c r="AP261" s="1"/>
       <c r="AQ261" s="1"/>
@@ -23577,7 +23584,7 @@
       <c r="AK262" s="1"/>
       <c r="AL262" s="1"/>
       <c r="AM262" s="1"/>
-      <c r="AN262" s="1"/>
+      <c r="AN262" s="7"/>
       <c r="AO262" s="1"/>
       <c r="AP262" s="1"/>
       <c r="AQ262" s="1"/>
@@ -23627,7 +23634,7 @@
       <c r="AK263" s="1"/>
       <c r="AL263" s="1"/>
       <c r="AM263" s="1"/>
-      <c r="AN263" s="1"/>
+      <c r="AN263" s="7"/>
       <c r="AO263" s="1"/>
       <c r="AP263" s="1"/>
       <c r="AQ263" s="1"/>
@@ -23677,7 +23684,7 @@
       <c r="AK264" s="1"/>
       <c r="AL264" s="1"/>
       <c r="AM264" s="1"/>
-      <c r="AN264" s="1"/>
+      <c r="AN264" s="7"/>
       <c r="AO264" s="1"/>
       <c r="AP264" s="1"/>
       <c r="AQ264" s="1"/>
@@ -23727,7 +23734,7 @@
       <c r="AK265" s="1"/>
       <c r="AL265" s="1"/>
       <c r="AM265" s="1"/>
-      <c r="AN265" s="1"/>
+      <c r="AN265" s="7"/>
       <c r="AO265" s="1"/>
       <c r="AP265" s="1"/>
       <c r="AQ265" s="1"/>
@@ -23777,7 +23784,7 @@
       <c r="AK266" s="1"/>
       <c r="AL266" s="1"/>
       <c r="AM266" s="1"/>
-      <c r="AN266" s="1"/>
+      <c r="AN266" s="7"/>
       <c r="AO266" s="1"/>
       <c r="AP266" s="1"/>
       <c r="AQ266" s="1"/>
@@ -23827,7 +23834,7 @@
       <c r="AK267" s="1"/>
       <c r="AL267" s="1"/>
       <c r="AM267" s="1"/>
-      <c r="AN267" s="1"/>
+      <c r="AN267" s="7"/>
       <c r="AO267" s="1"/>
       <c r="AP267" s="1"/>
       <c r="AQ267" s="1"/>
@@ -23877,7 +23884,7 @@
       <c r="AK268" s="1"/>
       <c r="AL268" s="1"/>
       <c r="AM268" s="1"/>
-      <c r="AN268" s="1"/>
+      <c r="AN268" s="7"/>
       <c r="AO268" s="1"/>
       <c r="AP268" s="1"/>
       <c r="AQ268" s="1"/>
@@ -23927,7 +23934,7 @@
       <c r="AK269" s="1"/>
       <c r="AL269" s="1"/>
       <c r="AM269" s="1"/>
-      <c r="AN269" s="1"/>
+      <c r="AN269" s="7"/>
       <c r="AO269" s="1"/>
       <c r="AP269" s="1"/>
       <c r="AQ269" s="1"/>
@@ -23977,7 +23984,7 @@
       <c r="AK270" s="1"/>
       <c r="AL270" s="1"/>
       <c r="AM270" s="1"/>
-      <c r="AN270" s="1"/>
+      <c r="AN270" s="7"/>
       <c r="AO270" s="1"/>
       <c r="AP270" s="1"/>
       <c r="AQ270" s="1"/>
@@ -24027,7 +24034,7 @@
       <c r="AK271" s="1"/>
       <c r="AL271" s="1"/>
       <c r="AM271" s="1"/>
-      <c r="AN271" s="1"/>
+      <c r="AN271" s="7"/>
       <c r="AO271" s="1"/>
       <c r="AP271" s="1"/>
       <c r="AQ271" s="1"/>
@@ -24077,7 +24084,7 @@
       <c r="AK272" s="1"/>
       <c r="AL272" s="1"/>
       <c r="AM272" s="1"/>
-      <c r="AN272" s="1"/>
+      <c r="AN272" s="7"/>
       <c r="AO272" s="1"/>
       <c r="AP272" s="1"/>
       <c r="AQ272" s="1"/>
@@ -24127,7 +24134,7 @@
       <c r="AK273" s="1"/>
       <c r="AL273" s="1"/>
       <c r="AM273" s="1"/>
-      <c r="AN273" s="1"/>
+      <c r="AN273" s="7"/>
       <c r="AO273" s="1"/>
       <c r="AP273" s="1"/>
       <c r="AQ273" s="1"/>
@@ -24177,7 +24184,7 @@
       <c r="AK274" s="1"/>
       <c r="AL274" s="1"/>
       <c r="AM274" s="1"/>
-      <c r="AN274" s="1"/>
+      <c r="AN274" s="7"/>
       <c r="AO274" s="1"/>
       <c r="AP274" s="1"/>
       <c r="AQ274" s="1"/>
@@ -24227,7 +24234,7 @@
       <c r="AK275" s="1"/>
       <c r="AL275" s="1"/>
       <c r="AM275" s="1"/>
-      <c r="AN275" s="1"/>
+      <c r="AN275" s="7"/>
       <c r="AO275" s="1"/>
       <c r="AP275" s="1"/>
       <c r="AQ275" s="1"/>
@@ -24277,7 +24284,7 @@
       <c r="AK276" s="1"/>
       <c r="AL276" s="1"/>
       <c r="AM276" s="1"/>
-      <c r="AN276" s="1"/>
+      <c r="AN276" s="7"/>
       <c r="AO276" s="1"/>
       <c r="AP276" s="1"/>
       <c r="AQ276" s="1"/>
@@ -24327,7 +24334,7 @@
       <c r="AK277" s="1"/>
       <c r="AL277" s="1"/>
       <c r="AM277" s="1"/>
-      <c r="AN277" s="1"/>
+      <c r="AN277" s="7"/>
       <c r="AO277" s="1"/>
       <c r="AP277" s="1"/>
       <c r="AQ277" s="1"/>
@@ -24377,7 +24384,7 @@
       <c r="AK278" s="1"/>
       <c r="AL278" s="1"/>
       <c r="AM278" s="1"/>
-      <c r="AN278" s="1"/>
+      <c r="AN278" s="7"/>
       <c r="AO278" s="1"/>
       <c r="AP278" s="1"/>
       <c r="AQ278" s="1"/>
@@ -24427,7 +24434,7 @@
       <c r="AK279" s="1"/>
       <c r="AL279" s="1"/>
       <c r="AM279" s="1"/>
-      <c r="AN279" s="1"/>
+      <c r="AN279" s="7"/>
       <c r="AO279" s="1"/>
       <c r="AP279" s="1"/>
       <c r="AQ279" s="1"/>
@@ -24477,7 +24484,7 @@
       <c r="AK280" s="1"/>
       <c r="AL280" s="1"/>
       <c r="AM280" s="1"/>
-      <c r="AN280" s="1"/>
+      <c r="AN280" s="7"/>
       <c r="AO280" s="1"/>
       <c r="AP280" s="1"/>
       <c r="AQ280" s="1"/>
@@ -24527,7 +24534,7 @@
       <c r="AK281" s="1"/>
       <c r="AL281" s="1"/>
       <c r="AM281" s="1"/>
-      <c r="AN281" s="1"/>
+      <c r="AN281" s="7"/>
       <c r="AO281" s="1"/>
       <c r="AP281" s="1"/>
       <c r="AQ281" s="1"/>
@@ -24577,7 +24584,7 @@
       <c r="AK282" s="1"/>
       <c r="AL282" s="1"/>
       <c r="AM282" s="1"/>
-      <c r="AN282" s="1"/>
+      <c r="AN282" s="7"/>
       <c r="AO282" s="1"/>
       <c r="AP282" s="1"/>
       <c r="AQ282" s="1"/>
@@ -24627,7 +24634,7 @@
       <c r="AK283" s="1"/>
       <c r="AL283" s="1"/>
       <c r="AM283" s="1"/>
-      <c r="AN283" s="1"/>
+      <c r="AN283" s="7"/>
       <c r="AO283" s="1"/>
       <c r="AP283" s="1"/>
       <c r="AQ283" s="1"/>
@@ -24677,7 +24684,7 @@
       <c r="AK284" s="1"/>
       <c r="AL284" s="1"/>
       <c r="AM284" s="1"/>
-      <c r="AN284" s="1"/>
+      <c r="AN284" s="7"/>
       <c r="AO284" s="1"/>
       <c r="AP284" s="1"/>
       <c r="AQ284" s="1"/>
@@ -24727,7 +24734,7 @@
       <c r="AK285" s="1"/>
       <c r="AL285" s="1"/>
       <c r="AM285" s="1"/>
-      <c r="AN285" s="1"/>
+      <c r="AN285" s="7"/>
       <c r="AO285" s="1"/>
       <c r="AP285" s="1"/>
       <c r="AQ285" s="1"/>
@@ -24777,7 +24784,7 @@
       <c r="AK286" s="1"/>
       <c r="AL286" s="1"/>
       <c r="AM286" s="1"/>
-      <c r="AN286" s="1"/>
+      <c r="AN286" s="7"/>
       <c r="AO286" s="1"/>
       <c r="AP286" s="1"/>
       <c r="AQ286" s="1"/>
@@ -24827,7 +24834,7 @@
       <c r="AK287" s="1"/>
       <c r="AL287" s="1"/>
       <c r="AM287" s="1"/>
-      <c r="AN287" s="1"/>
+      <c r="AN287" s="7"/>
       <c r="AO287" s="1"/>
       <c r="AP287" s="1"/>
       <c r="AQ287" s="1"/>
@@ -24877,7 +24884,7 @@
       <c r="AK288" s="1"/>
       <c r="AL288" s="1"/>
       <c r="AM288" s="1"/>
-      <c r="AN288" s="1"/>
+      <c r="AN288" s="7"/>
       <c r="AO288" s="1"/>
       <c r="AP288" s="1"/>
       <c r="AQ288" s="1"/>
@@ -24927,7 +24934,7 @@
       <c r="AK289" s="1"/>
       <c r="AL289" s="1"/>
       <c r="AM289" s="1"/>
-      <c r="AN289" s="1"/>
+      <c r="AN289" s="7"/>
       <c r="AO289" s="1"/>
       <c r="AP289" s="1"/>
       <c r="AQ289" s="1"/>
@@ -24977,7 +24984,7 @@
       <c r="AK290" s="1"/>
       <c r="AL290" s="1"/>
       <c r="AM290" s="1"/>
-      <c r="AN290" s="1"/>
+      <c r="AN290" s="7"/>
       <c r="AO290" s="1"/>
       <c r="AP290" s="1"/>
       <c r="AQ290" s="1"/>
@@ -25027,7 +25034,7 @@
       <c r="AK291" s="1"/>
       <c r="AL291" s="1"/>
       <c r="AM291" s="1"/>
-      <c r="AN291" s="1"/>
+      <c r="AN291" s="7"/>
       <c r="AO291" s="1"/>
       <c r="AP291" s="1"/>
       <c r="AQ291" s="1"/>
@@ -25077,7 +25084,7 @@
       <c r="AK292" s="1"/>
       <c r="AL292" s="1"/>
       <c r="AM292" s="1"/>
-      <c r="AN292" s="1"/>
+      <c r="AN292" s="7"/>
       <c r="AO292" s="1"/>
       <c r="AP292" s="1"/>
       <c r="AQ292" s="1"/>
@@ -25127,7 +25134,7 @@
       <c r="AK293" s="1"/>
       <c r="AL293" s="1"/>
       <c r="AM293" s="1"/>
-      <c r="AN293" s="1"/>
+      <c r="AN293" s="7"/>
       <c r="AO293" s="1"/>
       <c r="AP293" s="1"/>
       <c r="AQ293" s="1"/>
@@ -25177,7 +25184,7 @@
       <c r="AK294" s="1"/>
       <c r="AL294" s="1"/>
       <c r="AM294" s="1"/>
-      <c r="AN294" s="1"/>
+      <c r="AN294" s="7"/>
       <c r="AO294" s="1"/>
       <c r="AP294" s="1"/>
       <c r="AQ294" s="1"/>
@@ -25227,7 +25234,7 @@
       <c r="AK295" s="1"/>
       <c r="AL295" s="1"/>
       <c r="AM295" s="1"/>
-      <c r="AN295" s="1"/>
+      <c r="AN295" s="7"/>
       <c r="AO295" s="1"/>
       <c r="AP295" s="1"/>
       <c r="AQ295" s="1"/>
@@ -25277,7 +25284,7 @@
       <c r="AK296" s="1"/>
       <c r="AL296" s="1"/>
       <c r="AM296" s="1"/>
-      <c r="AN296" s="1"/>
+      <c r="AN296" s="7"/>
       <c r="AO296" s="1"/>
       <c r="AP296" s="1"/>
       <c r="AQ296" s="1"/>
@@ -25327,7 +25334,7 @@
       <c r="AK297" s="1"/>
       <c r="AL297" s="1"/>
       <c r="AM297" s="1"/>
-      <c r="AN297" s="1"/>
+      <c r="AN297" s="7"/>
       <c r="AO297" s="1"/>
       <c r="AP297" s="1"/>
       <c r="AQ297" s="1"/>
@@ -25377,7 +25384,7 @@
       <c r="AK298" s="1"/>
       <c r="AL298" s="1"/>
       <c r="AM298" s="1"/>
-      <c r="AN298" s="1"/>
+      <c r="AN298" s="7"/>
       <c r="AO298" s="1"/>
       <c r="AP298" s="1"/>
       <c r="AQ298" s="1"/>
@@ -25427,7 +25434,7 @@
       <c r="AK299" s="1"/>
       <c r="AL299" s="1"/>
       <c r="AM299" s="1"/>
-      <c r="AN299" s="1"/>
+      <c r="AN299" s="7"/>
       <c r="AO299" s="1"/>
       <c r="AP299" s="1"/>
       <c r="AQ299" s="1"/>
@@ -25477,7 +25484,7 @@
       <c r="AK300" s="1"/>
       <c r="AL300" s="1"/>
       <c r="AM300" s="1"/>
-      <c r="AN300" s="1"/>
+      <c r="AN300" s="7"/>
       <c r="AO300" s="1"/>
       <c r="AP300" s="1"/>
       <c r="AQ300" s="1"/>
@@ -25527,7 +25534,7 @@
       <c r="AK301" s="1"/>
       <c r="AL301" s="1"/>
       <c r="AM301" s="1"/>
-      <c r="AN301" s="1"/>
+      <c r="AN301" s="7"/>
       <c r="AO301" s="1"/>
       <c r="AP301" s="1"/>
       <c r="AQ301" s="1"/>
@@ -25577,7 +25584,7 @@
       <c r="AK302" s="1"/>
       <c r="AL302" s="1"/>
       <c r="AM302" s="1"/>
-      <c r="AN302" s="1"/>
+      <c r="AN302" s="7"/>
       <c r="AO302" s="1"/>
       <c r="AP302" s="1"/>
       <c r="AQ302" s="1"/>
@@ -25627,7 +25634,7 @@
       <c r="AK303" s="1"/>
       <c r="AL303" s="1"/>
       <c r="AM303" s="1"/>
-      <c r="AN303" s="1"/>
+      <c r="AN303" s="7"/>
       <c r="AO303" s="1"/>
       <c r="AP303" s="1"/>
       <c r="AQ303" s="1"/>
@@ -25677,7 +25684,7 @@
       <c r="AK304" s="1"/>
       <c r="AL304" s="1"/>
       <c r="AM304" s="1"/>
-      <c r="AN304" s="1"/>
+      <c r="AN304" s="7"/>
       <c r="AO304" s="1"/>
       <c r="AP304" s="1"/>
       <c r="AQ304" s="1"/>
@@ -25727,7 +25734,7 @@
       <c r="AK305" s="1"/>
       <c r="AL305" s="1"/>
       <c r="AM305" s="1"/>
-      <c r="AN305" s="1"/>
+      <c r="AN305" s="7"/>
       <c r="AO305" s="1"/>
       <c r="AP305" s="1"/>
       <c r="AQ305" s="1"/>
@@ -25777,7 +25784,7 @@
       <c r="AK306" s="1"/>
       <c r="AL306" s="1"/>
       <c r="AM306" s="1"/>
-      <c r="AN306" s="1"/>
+      <c r="AN306" s="7"/>
       <c r="AO306" s="1"/>
       <c r="AP306" s="1"/>
       <c r="AQ306" s="1"/>
@@ -25827,7 +25834,7 @@
       <c r="AK307" s="1"/>
       <c r="AL307" s="1"/>
       <c r="AM307" s="1"/>
-      <c r="AN307" s="1"/>
+      <c r="AN307" s="7"/>
       <c r="AO307" s="1"/>
       <c r="AP307" s="1"/>
       <c r="AQ307" s="1"/>
@@ -25877,7 +25884,7 @@
       <c r="AK308" s="1"/>
       <c r="AL308" s="1"/>
       <c r="AM308" s="1"/>
-      <c r="AN308" s="1"/>
+      <c r="AN308" s="7"/>
       <c r="AO308" s="1"/>
       <c r="AP308" s="1"/>
       <c r="AQ308" s="1"/>
@@ -25927,7 +25934,7 @@
       <c r="AK309" s="1"/>
       <c r="AL309" s="1"/>
       <c r="AM309" s="1"/>
-      <c r="AN309" s="1"/>
+      <c r="AN309" s="7"/>
       <c r="AO309" s="1"/>
       <c r="AP309" s="1"/>
       <c r="AQ309" s="1"/>
@@ -25977,7 +25984,7 @@
       <c r="AK310" s="1"/>
       <c r="AL310" s="1"/>
       <c r="AM310" s="1"/>
-      <c r="AN310" s="1"/>
+      <c r="AN310" s="7"/>
       <c r="AO310" s="1"/>
       <c r="AP310" s="1"/>
       <c r="AQ310" s="1"/>
@@ -26027,7 +26034,7 @@
       <c r="AK311" s="1"/>
       <c r="AL311" s="1"/>
       <c r="AM311" s="1"/>
-      <c r="AN311" s="1"/>
+      <c r="AN311" s="7"/>
       <c r="AO311" s="1"/>
       <c r="AP311" s="1"/>
       <c r="AQ311" s="1"/>
@@ -26077,7 +26084,7 @@
       <c r="AK312" s="1"/>
       <c r="AL312" s="1"/>
       <c r="AM312" s="1"/>
-      <c r="AN312" s="1"/>
+      <c r="AN312" s="7"/>
       <c r="AO312" s="1"/>
       <c r="AP312" s="1"/>
       <c r="AQ312" s="1"/>
@@ -26127,7 +26134,7 @@
       <c r="AK313" s="1"/>
       <c r="AL313" s="1"/>
       <c r="AM313" s="1"/>
-      <c r="AN313" s="1"/>
+      <c r="AN313" s="7"/>
       <c r="AO313" s="1"/>
       <c r="AP313" s="1"/>
       <c r="AQ313" s="1"/>
@@ -26177,7 +26184,7 @@
       <c r="AK314" s="1"/>
       <c r="AL314" s="1"/>
       <c r="AM314" s="1"/>
-      <c r="AN314" s="1"/>
+      <c r="AN314" s="7"/>
       <c r="AO314" s="1"/>
       <c r="AP314" s="1"/>
       <c r="AQ314" s="1"/>
@@ -26227,7 +26234,7 @@
       <c r="AK315" s="1"/>
       <c r="AL315" s="1"/>
       <c r="AM315" s="1"/>
-      <c r="AN315" s="1"/>
+      <c r="AN315" s="7"/>
       <c r="AO315" s="1"/>
       <c r="AP315" s="1"/>
       <c r="AQ315" s="1"/>
@@ -26277,7 +26284,7 @@
       <c r="AK316" s="1"/>
       <c r="AL316" s="1"/>
       <c r="AM316" s="1"/>
-      <c r="AN316" s="1"/>
+      <c r="AN316" s="7"/>
       <c r="AO316" s="1"/>
       <c r="AP316" s="1"/>
       <c r="AQ316" s="1"/>
@@ -26327,7 +26334,7 @@
       <c r="AK317" s="1"/>
       <c r="AL317" s="1"/>
       <c r="AM317" s="1"/>
-      <c r="AN317" s="1"/>
+      <c r="AN317" s="7"/>
       <c r="AO317" s="1"/>
       <c r="AP317" s="1"/>
       <c r="AQ317" s="1"/>
@@ -26377,7 +26384,7 @@
       <c r="AK318" s="1"/>
       <c r="AL318" s="1"/>
       <c r="AM318" s="1"/>
-      <c r="AN318" s="1"/>
+      <c r="AN318" s="7"/>
       <c r="AO318" s="1"/>
       <c r="AP318" s="1"/>
       <c r="AQ318" s="1"/>
@@ -26427,7 +26434,7 @@
       <c r="AK319" s="1"/>
       <c r="AL319" s="1"/>
       <c r="AM319" s="1"/>
-      <c r="AN319" s="1"/>
+      <c r="AN319" s="7"/>
       <c r="AO319" s="1"/>
       <c r="AP319" s="1"/>
       <c r="AQ319" s="1"/>
@@ -26477,7 +26484,7 @@
       <c r="AK320" s="1"/>
       <c r="AL320" s="1"/>
       <c r="AM320" s="1"/>
-      <c r="AN320" s="1"/>
+      <c r="AN320" s="7"/>
       <c r="AO320" s="1"/>
       <c r="AP320" s="1"/>
       <c r="AQ320" s="1"/>
@@ -26527,7 +26534,7 @@
       <c r="AK321" s="1"/>
       <c r="AL321" s="1"/>
       <c r="AM321" s="1"/>
-      <c r="AN321" s="1"/>
+      <c r="AN321" s="7"/>
       <c r="AO321" s="1"/>
       <c r="AP321" s="1"/>
       <c r="AQ321" s="1"/>
@@ -26577,7 +26584,7 @@
       <c r="AK322" s="1"/>
       <c r="AL322" s="1"/>
       <c r="AM322" s="1"/>
-      <c r="AN322" s="1"/>
+      <c r="AN322" s="7"/>
       <c r="AO322" s="1"/>
       <c r="AP322" s="1"/>
       <c r="AQ322" s="1"/>
@@ -26627,7 +26634,7 @@
       <c r="AK323" s="1"/>
       <c r="AL323" s="1"/>
       <c r="AM323" s="1"/>
-      <c r="AN323" s="1"/>
+      <c r="AN323" s="7"/>
       <c r="AO323" s="1"/>
       <c r="AP323" s="1"/>
       <c r="AQ323" s="1"/>
@@ -26677,7 +26684,7 @@
       <c r="AK324" s="1"/>
       <c r="AL324" s="1"/>
       <c r="AM324" s="1"/>
-      <c r="AN324" s="1"/>
+      <c r="AN324" s="7"/>
       <c r="AO324" s="1"/>
       <c r="AP324" s="1"/>
       <c r="AQ324" s="1"/>
@@ -26727,7 +26734,7 @@
       <c r="AK325" s="1"/>
       <c r="AL325" s="1"/>
       <c r="AM325" s="1"/>
-      <c r="AN325" s="1"/>
+      <c r="AN325" s="7"/>
       <c r="AO325" s="1"/>
       <c r="AP325" s="1"/>
       <c r="AQ325" s="1"/>
@@ -26777,7 +26784,7 @@
       <c r="AK326" s="1"/>
       <c r="AL326" s="1"/>
       <c r="AM326" s="1"/>
-      <c r="AN326" s="1"/>
+      <c r="AN326" s="7"/>
       <c r="AO326" s="1"/>
       <c r="AP326" s="1"/>
       <c r="AQ326" s="1"/>
@@ -26827,7 +26834,7 @@
       <c r="AK327" s="1"/>
       <c r="AL327" s="1"/>
       <c r="AM327" s="1"/>
-      <c r="AN327" s="1"/>
+      <c r="AN327" s="7"/>
       <c r="AO327" s="1"/>
       <c r="AP327" s="1"/>
       <c r="AQ327" s="1"/>
@@ -26877,7 +26884,7 @@
       <c r="AK328" s="1"/>
       <c r="AL328" s="1"/>
       <c r="AM328" s="1"/>
-      <c r="AN328" s="1"/>
+      <c r="AN328" s="7"/>
       <c r="AO328" s="1"/>
       <c r="AP328" s="1"/>
       <c r="AQ328" s="1"/>
@@ -26927,7 +26934,7 @@
       <c r="AK329" s="1"/>
       <c r="AL329" s="1"/>
       <c r="AM329" s="1"/>
-      <c r="AN329" s="1"/>
+      <c r="AN329" s="7"/>
       <c r="AO329" s="1"/>
       <c r="AP329" s="1"/>
       <c r="AQ329" s="1"/>
@@ -26977,7 +26984,7 @@
       <c r="AK330" s="1"/>
       <c r="AL330" s="1"/>
       <c r="AM330" s="1"/>
-      <c r="AN330" s="1"/>
+      <c r="AN330" s="7"/>
       <c r="AO330" s="1"/>
       <c r="AP330" s="1"/>
       <c r="AQ330" s="1"/>
@@ -27027,7 +27034,7 @@
       <c r="AK331" s="1"/>
       <c r="AL331" s="1"/>
       <c r="AM331" s="1"/>
-      <c r="AN331" s="1"/>
+      <c r="AN331" s="7"/>
       <c r="AO331" s="1"/>
       <c r="AP331" s="1"/>
       <c r="AQ331" s="1"/>
@@ -27077,7 +27084,7 @@
       <c r="AK332" s="1"/>
       <c r="AL332" s="1"/>
       <c r="AM332" s="1"/>
-      <c r="AN332" s="1"/>
+      <c r="AN332" s="7"/>
       <c r="AO332" s="1"/>
       <c r="AP332" s="1"/>
       <c r="AQ332" s="1"/>
@@ -27127,7 +27134,7 @@
       <c r="AK333" s="1"/>
       <c r="AL333" s="1"/>
       <c r="AM333" s="1"/>
-      <c r="AN333" s="1"/>
+      <c r="AN333" s="7"/>
       <c r="AO333" s="1"/>
       <c r="AP333" s="1"/>
       <c r="AQ333" s="1"/>
@@ -27177,7 +27184,7 @@
       <c r="AK334" s="1"/>
       <c r="AL334" s="1"/>
       <c r="AM334" s="1"/>
-      <c r="AN334" s="1"/>
+      <c r="AN334" s="7"/>
       <c r="AO334" s="1"/>
       <c r="AP334" s="1"/>
       <c r="AQ334" s="1"/>
@@ -27227,7 +27234,7 @@
       <c r="AK335" s="1"/>
       <c r="AL335" s="1"/>
       <c r="AM335" s="1"/>
-      <c r="AN335" s="1"/>
+      <c r="AN335" s="7"/>
       <c r="AO335" s="1"/>
       <c r="AP335" s="1"/>
       <c r="AQ335" s="1"/>
@@ -27277,7 +27284,7 @@
       <c r="AK336" s="1"/>
       <c r="AL336" s="1"/>
       <c r="AM336" s="1"/>
-      <c r="AN336" s="1"/>
+      <c r="AN336" s="7"/>
       <c r="AO336" s="1"/>
       <c r="AP336" s="1"/>
       <c r="AQ336" s="1"/>
@@ -27327,7 +27334,7 @@
       <c r="AK337" s="1"/>
       <c r="AL337" s="1"/>
       <c r="AM337" s="1"/>
-      <c r="AN337" s="1"/>
+      <c r="AN337" s="7"/>
       <c r="AO337" s="1"/>
       <c r="AP337" s="1"/>
       <c r="AQ337" s="1"/>
@@ -27377,7 +27384,7 @@
       <c r="AK338" s="1"/>
       <c r="AL338" s="1"/>
       <c r="AM338" s="1"/>
-      <c r="AN338" s="1"/>
+      <c r="AN338" s="7"/>
       <c r="AO338" s="1"/>
       <c r="AP338" s="1"/>
       <c r="AQ338" s="1"/>
@@ -27427,7 +27434,7 @@
       <c r="AK339" s="1"/>
       <c r="AL339" s="1"/>
       <c r="AM339" s="1"/>
-      <c r="AN339" s="1"/>
+      <c r="AN339" s="7"/>
       <c r="AO339" s="1"/>
       <c r="AP339" s="1"/>
       <c r="AQ339" s="1"/>
@@ -27477,7 +27484,7 @@
       <c r="AK340" s="1"/>
       <c r="AL340" s="1"/>
       <c r="AM340" s="1"/>
-      <c r="AN340" s="1"/>
+      <c r="AN340" s="7"/>
       <c r="AO340" s="1"/>
       <c r="AP340" s="1"/>
       <c r="AQ340" s="1"/>
@@ -27527,7 +27534,7 @@
       <c r="AK341" s="1"/>
       <c r="AL341" s="1"/>
       <c r="AM341" s="1"/>
-      <c r="AN341" s="1"/>
+      <c r="AN341" s="7"/>
       <c r="AO341" s="1"/>
       <c r="AP341" s="1"/>
       <c r="AQ341" s="1"/>
@@ -27577,7 +27584,7 @@
       <c r="AK342" s="1"/>
       <c r="AL342" s="1"/>
       <c r="AM342" s="1"/>
-      <c r="AN342" s="1"/>
+      <c r="AN342" s="7"/>
       <c r="AO342" s="1"/>
       <c r="AP342" s="1"/>
       <c r="AQ342" s="1"/>
@@ -27627,7 +27634,7 @@
       <c r="AK343" s="1"/>
       <c r="AL343" s="1"/>
       <c r="AM343" s="1"/>
-      <c r="AN343" s="1"/>
+      <c r="AN343" s="7"/>
       <c r="AO343" s="1"/>
       <c r="AP343" s="1"/>
       <c r="AQ343" s="1"/>
@@ -27677,7 +27684,7 @@
       <c r="AK344" s="1"/>
       <c r="AL344" s="1"/>
       <c r="AM344" s="1"/>
-      <c r="AN344" s="1"/>
+      <c r="AN344" s="7"/>
       <c r="AO344" s="1"/>
       <c r="AP344" s="1"/>
       <c r="AQ344" s="1"/>
@@ -27727,7 +27734,7 @@
       <c r="AK345" s="1"/>
       <c r="AL345" s="1"/>
       <c r="AM345" s="1"/>
-      <c r="AN345" s="1"/>
+      <c r="AN345" s="7"/>
       <c r="AO345" s="1"/>
       <c r="AP345" s="1"/>
       <c r="AQ345" s="1"/>
@@ -27777,7 +27784,7 @@
       <c r="AK346" s="1"/>
       <c r="AL346" s="1"/>
       <c r="AM346" s="1"/>
-      <c r="AN346" s="1"/>
+      <c r="AN346" s="7"/>
       <c r="AO346" s="1"/>
       <c r="AP346" s="1"/>
       <c r="AQ346" s="1"/>
@@ -27827,7 +27834,7 @@
       <c r="AK347" s="1"/>
       <c r="AL347" s="1"/>
       <c r="AM347" s="1"/>
-      <c r="AN347" s="1"/>
+      <c r="AN347" s="7"/>
       <c r="AO347" s="1"/>
       <c r="AP347" s="1"/>
       <c r="AQ347" s="1"/>
@@ -27877,7 +27884,7 @@
       <c r="AK348" s="1"/>
       <c r="AL348" s="1"/>
       <c r="AM348" s="1"/>
-      <c r="AN348" s="1"/>
+      <c r="AN348" s="7"/>
       <c r="AO348" s="1"/>
       <c r="AP348" s="1"/>
       <c r="AQ348" s="1"/>
@@ -27927,7 +27934,7 @@
       <c r="AK349" s="1"/>
       <c r="AL349" s="1"/>
       <c r="AM349" s="1"/>
-      <c r="AN349" s="1"/>
+      <c r="AN349" s="7"/>
       <c r="AO349" s="1"/>
       <c r="AP349" s="1"/>
       <c r="AQ349" s="1"/>
@@ -27977,7 +27984,7 @@
       <c r="AK350" s="1"/>
       <c r="AL350" s="1"/>
       <c r="AM350" s="1"/>
-      <c r="AN350" s="1"/>
+      <c r="AN350" s="7"/>
       <c r="AO350" s="1"/>
       <c r="AP350" s="1"/>
       <c r="AQ350" s="1"/>
@@ -28027,7 +28034,7 @@
       <c r="AK351" s="1"/>
       <c r="AL351" s="1"/>
       <c r="AM351" s="1"/>
-      <c r="AN351" s="1"/>
+      <c r="AN351" s="7"/>
       <c r="AO351" s="1"/>
       <c r="AP351" s="1"/>
       <c r="AQ351" s="1"/>
@@ -28077,7 +28084,7 @@
       <c r="AK352" s="1"/>
       <c r="AL352" s="1"/>
       <c r="AM352" s="1"/>
-      <c r="AN352" s="1"/>
+      <c r="AN352" s="7"/>
       <c r="AO352" s="1"/>
       <c r="AP352" s="1"/>
       <c r="AQ352" s="1"/>
@@ -28127,7 +28134,7 @@
       <c r="AK353" s="1"/>
       <c r="AL353" s="1"/>
       <c r="AM353" s="1"/>
-      <c r="AN353" s="1"/>
+      <c r="AN353" s="7"/>
       <c r="AO353" s="1"/>
       <c r="AP353" s="1"/>
       <c r="AQ353" s="1"/>
@@ -28177,7 +28184,7 @@
       <c r="AK354" s="1"/>
       <c r="AL354" s="1"/>
       <c r="AM354" s="1"/>
-      <c r="AN354" s="1"/>
+      <c r="AN354" s="7"/>
       <c r="AO354" s="1"/>
       <c r="AP354" s="1"/>
       <c r="AQ354" s="1"/>
@@ -28227,7 +28234,7 @@
       <c r="AK355" s="1"/>
       <c r="AL355" s="1"/>
       <c r="AM355" s="1"/>
-      <c r="AN355" s="1"/>
+      <c r="AN355" s="7"/>
       <c r="AO355" s="1"/>
       <c r="AP355" s="1"/>
       <c r="AQ355" s="1"/>
@@ -28277,7 +28284,7 @@
       <c r="AK356" s="1"/>
       <c r="AL356" s="1"/>
       <c r="AM356" s="1"/>
-      <c r="AN356" s="1"/>
+      <c r="AN356" s="7"/>
       <c r="AO356" s="1"/>
       <c r="AP356" s="1"/>
       <c r="AQ356" s="1"/>
@@ -28327,7 +28334,7 @@
       <c r="AK357" s="1"/>
       <c r="AL357" s="1"/>
       <c r="AM357" s="1"/>
-      <c r="AN357" s="1"/>
+      <c r="AN357" s="7"/>
       <c r="AO357" s="1"/>
       <c r="AP357" s="1"/>
       <c r="AQ357" s="1"/>
@@ -28377,7 +28384,7 @@
       <c r="AK358" s="1"/>
       <c r="AL358" s="1"/>
       <c r="AM358" s="1"/>
-      <c r="AN358" s="1"/>
+      <c r="AN358" s="7"/>
       <c r="AO358" s="1"/>
       <c r="AP358" s="1"/>
       <c r="AQ358" s="1"/>
@@ -28427,7 +28434,7 @@
       <c r="AK359" s="1"/>
       <c r="AL359" s="1"/>
       <c r="AM359" s="1"/>
-      <c r="AN359" s="1"/>
+      <c r="AN359" s="7"/>
       <c r="AO359" s="1"/>
       <c r="AP359" s="1"/>
       <c r="AQ359" s="1"/>
@@ -28477,7 +28484,7 @@
       <c r="AK360" s="1"/>
       <c r="AL360" s="1"/>
       <c r="AM360" s="1"/>
-      <c r="AN360" s="1"/>
+      <c r="AN360" s="7"/>
       <c r="AO360" s="1"/>
       <c r="AP360" s="1"/>
       <c r="AQ360" s="1"/>
@@ -28527,7 +28534,7 @@
       <c r="AK361" s="1"/>
       <c r="AL361" s="1"/>
       <c r="AM361" s="1"/>
-      <c r="AN361" s="1"/>
+      <c r="AN361" s="7"/>
       <c r="AO361" s="1"/>
       <c r="AP361" s="1"/>
       <c r="AQ361" s="1"/>
@@ -28577,7 +28584,7 @@
       <c r="AK362" s="1"/>
       <c r="AL362" s="1"/>
       <c r="AM362" s="1"/>
-      <c r="AN362" s="1"/>
+      <c r="AN362" s="7"/>
       <c r="AO362" s="1"/>
       <c r="AP362" s="1"/>
       <c r="AQ362" s="1"/>
@@ -28627,7 +28634,7 @@
       <c r="AK363" s="1"/>
       <c r="AL363" s="1"/>
       <c r="AM363" s="1"/>
-      <c r="AN363" s="1"/>
+      <c r="AN363" s="7"/>
       <c r="AO363" s="1"/>
       <c r="AP363" s="1"/>
       <c r="AQ363" s="1"/>
@@ -28677,7 +28684,7 @@
       <c r="AK364" s="1"/>
       <c r="AL364" s="1"/>
       <c r="AM364" s="1"/>
-      <c r="AN364" s="1"/>
+      <c r="AN364" s="7"/>
       <c r="AO364" s="1"/>
       <c r="AP364" s="1"/>
       <c r="AQ364" s="1"/>
@@ -28727,7 +28734,7 @@
       <c r="AK365" s="1"/>
       <c r="AL365" s="1"/>
       <c r="AM365" s="1"/>
-      <c r="AN365" s="1"/>
+      <c r="AN365" s="7"/>
       <c r="AO365" s="1"/>
       <c r="AP365" s="1"/>
       <c r="AQ365" s="1"/>
@@ -28777,7 +28784,7 @@
       <c r="AK366" s="1"/>
       <c r="AL366" s="1"/>
       <c r="AM366" s="1"/>
-      <c r="AN366" s="1"/>
+      <c r="AN366" s="7"/>
       <c r="AO366" s="1"/>
       <c r="AP366" s="1"/>
       <c r="AQ366" s="1"/>
@@ -28827,7 +28834,7 @@
       <c r="AK367" s="1"/>
       <c r="AL367" s="1"/>
       <c r="AM367" s="1"/>
-      <c r="AN367" s="1"/>
+      <c r="AN367" s="7"/>
       <c r="AO367" s="1"/>
       <c r="AP367" s="1"/>
       <c r="AQ367" s="1"/>
@@ -28877,7 +28884,7 @@
       <c r="AK368" s="1"/>
       <c r="AL368" s="1"/>
       <c r="AM368" s="1"/>
-      <c r="AN368" s="1"/>
+      <c r="AN368" s="7"/>
       <c r="AO368" s="1"/>
       <c r="AP368" s="1"/>
       <c r="AQ368" s="1"/>
@@ -28927,7 +28934,7 @@
       <c r="AK369" s="1"/>
       <c r="AL369" s="1"/>
       <c r="AM369" s="1"/>
-      <c r="AN369" s="1"/>
+      <c r="AN369" s="7"/>
       <c r="AO369" s="1"/>
       <c r="AP369" s="1"/>
       <c r="AQ369" s="1"/>
@@ -28977,7 +28984,7 @@
       <c r="AK370" s="1"/>
       <c r="AL370" s="1"/>
       <c r="AM370" s="1"/>
-      <c r="AN370" s="1"/>
+      <c r="AN370" s="7"/>
       <c r="AO370" s="1"/>
       <c r="AP370" s="1"/>
       <c r="AQ370" s="1"/>
@@ -29027,7 +29034,7 @@
       <c r="AK371" s="1"/>
       <c r="AL371" s="1"/>
       <c r="AM371" s="1"/>
-      <c r="AN371" s="1"/>
+      <c r="AN371" s="7"/>
       <c r="AO371" s="1"/>
       <c r="AP371" s="1"/>
       <c r="AQ371" s="1"/>
@@ -29077,7 +29084,7 @@
       <c r="AK372" s="1"/>
       <c r="AL372" s="1"/>
       <c r="AM372" s="1"/>
-      <c r="AN372" s="1"/>
+      <c r="AN372" s="7"/>
       <c r="AO372" s="1"/>
       <c r="AP372" s="1"/>
       <c r="AQ372" s="1"/>
@@ -29127,7 +29134,7 @@
       <c r="AK373" s="1"/>
       <c r="AL373" s="1"/>
       <c r="AM373" s="1"/>
-      <c r="AN373" s="1"/>
+      <c r="AN373" s="7"/>
       <c r="AO373" s="1"/>
       <c r="AP373" s="1"/>
       <c r="AQ373" s="1"/>
@@ -29177,7 +29184,7 @@
       <c r="AK374" s="1"/>
       <c r="AL374" s="1"/>
       <c r="AM374" s="1"/>
-      <c r="AN374" s="1"/>
+      <c r="AN374" s="7"/>
       <c r="AO374" s="1"/>
       <c r="AP374" s="1"/>
       <c r="AQ374" s="1"/>
@@ -29227,7 +29234,7 @@
       <c r="AK375" s="1"/>
       <c r="AL375" s="1"/>
       <c r="AM375" s="1"/>
-      <c r="AN375" s="1"/>
+      <c r="AN375" s="7"/>
       <c r="AO375" s="1"/>
       <c r="AP375" s="1"/>
       <c r="AQ375" s="1"/>
@@ -29277,7 +29284,7 @@
       <c r="AK376" s="1"/>
       <c r="AL376" s="1"/>
       <c r="AM376" s="1"/>
-      <c r="AN376" s="1"/>
+      <c r="AN376" s="7"/>
       <c r="AO376" s="1"/>
       <c r="AP376" s="1"/>
       <c r="AQ376" s="1"/>
@@ -29327,7 +29334,7 @@
       <c r="AK377" s="1"/>
       <c r="AL377" s="1"/>
       <c r="AM377" s="1"/>
-      <c r="AN377" s="1"/>
+      <c r="AN377" s="7"/>
       <c r="AO377" s="1"/>
       <c r="AP377" s="1"/>
       <c r="AQ377" s="1"/>
@@ -29377,7 +29384,7 @@
       <c r="AK378" s="1"/>
       <c r="AL378" s="1"/>
       <c r="AM378" s="1"/>
-      <c r="AN378" s="1"/>
+      <c r="AN378" s="7"/>
       <c r="AO378" s="1"/>
       <c r="AP378" s="1"/>
       <c r="AQ378" s="1"/>
@@ -29427,7 +29434,7 @@
       <c r="AK379" s="1"/>
       <c r="AL379" s="1"/>
       <c r="AM379" s="1"/>
-      <c r="AN379" s="1"/>
+      <c r="AN379" s="7"/>
       <c r="AO379" s="1"/>
       <c r="AP379" s="1"/>
       <c r="AQ379" s="1"/>
@@ -29477,7 +29484,7 @@
       <c r="AK380" s="1"/>
       <c r="AL380" s="1"/>
       <c r="AM380" s="1"/>
-      <c r="AN380" s="1"/>
+      <c r="AN380" s="7"/>
       <c r="AO380" s="1"/>
       <c r="AP380" s="1"/>
       <c r="AQ380" s="1"/>
@@ -29527,7 +29534,7 @@
       <c r="AK381" s="1"/>
       <c r="AL381" s="1"/>
       <c r="AM381" s="1"/>
-      <c r="AN381" s="1"/>
+      <c r="AN381" s="7"/>
       <c r="AO381" s="1"/>
       <c r="AP381" s="1"/>
       <c r="AQ381" s="1"/>
@@ -29577,7 +29584,7 @@
       <c r="AK382" s="1"/>
       <c r="AL382" s="1"/>
       <c r="AM382" s="1"/>
-      <c r="AN382" s="1"/>
+      <c r="AN382" s="7"/>
       <c r="AO382" s="1"/>
       <c r="AP382" s="1"/>
       <c r="AQ382" s="1"/>
@@ -29627,7 +29634,7 @@
       <c r="AK383" s="1"/>
       <c r="AL383" s="1"/>
       <c r="AM383" s="1"/>
-      <c r="AN383" s="1"/>
+      <c r="AN383" s="7"/>
       <c r="AO383" s="1"/>
       <c r="AP383" s="1"/>
       <c r="AQ383" s="1"/>
@@ -29677,7 +29684,7 @@
       <c r="AK384" s="1"/>
       <c r="AL384" s="1"/>
       <c r="AM384" s="1"/>
-      <c r="AN384" s="1"/>
+      <c r="AN384" s="7"/>
       <c r="AO384" s="1"/>
       <c r="AP384" s="1"/>
       <c r="AQ384" s="1"/>
@@ -29727,7 +29734,7 @@
       <c r="AK385" s="1"/>
       <c r="AL385" s="1"/>
       <c r="AM385" s="1"/>
-      <c r="AN385" s="1"/>
+      <c r="AN385" s="7"/>
       <c r="AO385" s="1"/>
       <c r="AP385" s="1"/>
       <c r="AQ385" s="1"/>
@@ -29777,7 +29784,7 @@
       <c r="AK386" s="1"/>
       <c r="AL386" s="1"/>
       <c r="AM386" s="1"/>
-      <c r="AN386" s="1"/>
+      <c r="AN386" s="7"/>
       <c r="AO386" s="1"/>
       <c r="AP386" s="1"/>
       <c r="AQ386" s="1"/>
@@ -29827,7 +29834,7 @@
       <c r="AK387" s="1"/>
       <c r="AL387" s="1"/>
       <c r="AM387" s="1"/>
-      <c r="AN387" s="1"/>
+      <c r="AN387" s="7"/>
       <c r="AO387" s="1"/>
       <c r="AP387" s="1"/>
       <c r="AQ387" s="1"/>
@@ -29877,7 +29884,7 @@
       <c r="AK388" s="1"/>
       <c r="AL388" s="1"/>
       <c r="AM388" s="1"/>
-      <c r="AN388" s="1"/>
+      <c r="AN388" s="7"/>
       <c r="AO388" s="1"/>
       <c r="AP388" s="1"/>
       <c r="AQ388" s="1"/>
@@ -29927,7 +29934,7 @@
       <c r="AK389" s="1"/>
       <c r="AL389" s="1"/>
       <c r="AM389" s="1"/>
-      <c r="AN389" s="1"/>
+      <c r="AN389" s="7"/>
       <c r="AO389" s="1"/>
       <c r="AP389" s="1"/>
       <c r="AQ389" s="1"/>
@@ -29977,7 +29984,7 @@
       <c r="AK390" s="1"/>
       <c r="AL390" s="1"/>
       <c r="AM390" s="1"/>
-      <c r="AN390" s="1"/>
+      <c r="AN390" s="7"/>
       <c r="AO390" s="1"/>
       <c r="AP390" s="1"/>
       <c r="AQ390" s="1"/>
@@ -30027,7 +30034,7 @@
       <c r="AK391" s="1"/>
       <c r="AL391" s="1"/>
       <c r="AM391" s="1"/>
-      <c r="AN391" s="1"/>
+      <c r="AN391" s="7"/>
       <c r="AO391" s="1"/>
       <c r="AP391" s="1"/>
       <c r="AQ391" s="1"/>
@@ -30077,7 +30084,7 @@
       <c r="AK392" s="1"/>
       <c r="AL392" s="1"/>
       <c r="AM392" s="1"/>
-      <c r="AN392" s="1"/>
+      <c r="AN392" s="7"/>
       <c r="AO392" s="1"/>
       <c r="AP392" s="1"/>
       <c r="AQ392" s="1"/>
@@ -30127,7 +30134,7 @@
       <c r="AK393" s="1"/>
       <c r="AL393" s="1"/>
       <c r="AM393" s="1"/>
-      <c r="AN393" s="1"/>
+      <c r="AN393" s="7"/>
       <c r="AO393" s="1"/>
       <c r="AP393" s="1"/>
       <c r="AQ393" s="1"/>
@@ -30177,7 +30184,7 @@
       <c r="AK394" s="1"/>
       <c r="AL394" s="1"/>
       <c r="AM394" s="1"/>
-      <c r="AN394" s="1"/>
+      <c r="AN394" s="7"/>
       <c r="AO394" s="1"/>
       <c r="AP394" s="1"/>
       <c r="AQ394" s="1"/>
@@ -30227,7 +30234,7 @@
       <c r="AK395" s="1"/>
       <c r="AL395" s="1"/>
       <c r="AM395" s="1"/>
-      <c r="AN395" s="1"/>
+      <c r="AN395" s="7"/>
       <c r="AO395" s="1"/>
       <c r="AP395" s="1"/>
       <c r="AQ395" s="1"/>
@@ -30277,7 +30284,7 @@
       <c r="AK396" s="1"/>
       <c r="AL396" s="1"/>
       <c r="AM396" s="1"/>
-      <c r="AN396" s="1"/>
+      <c r="AN396" s="7"/>
       <c r="AO396" s="1"/>
       <c r="AP396" s="1"/>
       <c r="AQ396" s="1"/>
@@ -30327,7 +30334,7 @@
       <c r="AK397" s="1"/>
       <c r="AL397" s="1"/>
       <c r="AM397" s="1"/>
-      <c r="AN397" s="1"/>
+      <c r="AN397" s="7"/>
       <c r="AO397" s="1"/>
       <c r="AP397" s="1"/>
       <c r="AQ397" s="1"/>
@@ -30377,7 +30384,7 @@
       <c r="AK398" s="1"/>
       <c r="AL398" s="1"/>
       <c r="AM398" s="1"/>
-      <c r="AN398" s="1"/>
+      <c r="AN398" s="7"/>
       <c r="AO398" s="1"/>
       <c r="AP398" s="1"/>
       <c r="AQ398" s="1"/>
@@ -30427,7 +30434,7 @@
       <c r="AK399" s="1"/>
       <c r="AL399" s="1"/>
       <c r="AM399" s="1"/>
-      <c r="AN399" s="1"/>
+      <c r="AN399" s="7"/>
       <c r="AO399" s="1"/>
       <c r="AP399" s="1"/>
       <c r="AQ399" s="1"/>
@@ -30477,7 +30484,7 @@
       <c r="AK400" s="1"/>
       <c r="AL400" s="1"/>
       <c r="AM400" s="1"/>
-      <c r="AN400" s="1"/>
+      <c r="AN400" s="7"/>
       <c r="AO400" s="1"/>
       <c r="AP400" s="1"/>
       <c r="AQ400" s="1"/>
@@ -30527,7 +30534,7 @@
       <c r="AK401" s="1"/>
       <c r="AL401" s="1"/>
       <c r="AM401" s="1"/>
-      <c r="AN401" s="1"/>
+      <c r="AN401" s="7"/>
       <c r="AO401" s="1"/>
       <c r="AP401" s="1"/>
       <c r="AQ401" s="1"/>
@@ -30577,7 +30584,7 @@
       <c r="AK402" s="1"/>
       <c r="AL402" s="1"/>
       <c r="AM402" s="1"/>
-      <c r="AN402" s="1"/>
+      <c r="AN402" s="7"/>
       <c r="AO402" s="1"/>
       <c r="AP402" s="1"/>
       <c r="AQ402" s="1"/>
@@ -30627,7 +30634,7 @@
       <c r="AK403" s="1"/>
       <c r="AL403" s="1"/>
       <c r="AM403" s="1"/>
-      <c r="AN403" s="1"/>
+      <c r="AN403" s="7"/>
       <c r="AO403" s="1"/>
       <c r="AP403" s="1"/>
       <c r="AQ403" s="1"/>
@@ -30677,7 +30684,7 @@
       <c r="AK404" s="1"/>
       <c r="AL404" s="1"/>
       <c r="AM404" s="1"/>
-      <c r="AN404" s="1"/>
+      <c r="AN404" s="7"/>
       <c r="AO404" s="1"/>
       <c r="AP404" s="1"/>
       <c r="AQ404" s="1"/>
@@ -30727,7 +30734,7 @@
       <c r="AK405" s="1"/>
       <c r="AL405" s="1"/>
       <c r="AM405" s="1"/>
-      <c r="AN405" s="1"/>
+      <c r="AN405" s="7"/>
       <c r="AO405" s="1"/>
       <c r="AP405" s="1"/>
       <c r="AQ405" s="1"/>
@@ -30777,7 +30784,7 @@
       <c r="AK406" s="1"/>
       <c r="AL406" s="1"/>
       <c r="AM406" s="1"/>
-      <c r="AN406" s="1"/>
+      <c r="AN406" s="7"/>
       <c r="AO406" s="1"/>
       <c r="AP406" s="1"/>
       <c r="AQ406" s="1"/>
@@ -30827,7 +30834,7 @@
       <c r="AK407" s="1"/>
       <c r="AL407" s="1"/>
       <c r="AM407" s="1"/>
-      <c r="AN407" s="1"/>
+      <c r="AN407" s="7"/>
       <c r="AO407" s="1"/>
       <c r="AP407" s="1"/>
       <c r="AQ407" s="1"/>
@@ -30877,7 +30884,7 @@
       <c r="AK408" s="1"/>
       <c r="AL408" s="1"/>
       <c r="AM408" s="1"/>
-      <c r="AN408" s="1"/>
+      <c r="AN408" s="7"/>
       <c r="AO408" s="1"/>
       <c r="AP408" s="1"/>
       <c r="AQ408" s="1"/>
@@ -30927,7 +30934,7 @@
       <c r="AK409" s="1"/>
       <c r="AL409" s="1"/>
       <c r="AM409" s="1"/>
-      <c r="AN409" s="1"/>
+      <c r="AN409" s="7"/>
       <c r="AO409" s="1"/>
       <c r="AP409" s="1"/>
       <c r="AQ409" s="1"/>
@@ -30977,7 +30984,7 @@
       <c r="AK410" s="1"/>
       <c r="AL410" s="1"/>
       <c r="AM410" s="1"/>
-      <c r="AN410" s="1"/>
+      <c r="AN410" s="7"/>
       <c r="AO410" s="1"/>
       <c r="AP410" s="1"/>
       <c r="AQ410" s="1"/>
@@ -31027,7 +31034,7 @@
       <c r="AK411" s="1"/>
       <c r="AL411" s="1"/>
       <c r="AM411" s="1"/>
-      <c r="AN411" s="1"/>
+      <c r="AN411" s="7"/>
       <c r="AO411" s="1"/>
       <c r="AP411" s="1"/>
       <c r="AQ411" s="1"/>
@@ -31077,7 +31084,7 @@
       <c r="AK412" s="1"/>
       <c r="AL412" s="1"/>
       <c r="AM412" s="1"/>
-      <c r="AN412" s="1"/>
+      <c r="AN412" s="7"/>
       <c r="AO412" s="1"/>
       <c r="AP412" s="1"/>
       <c r="AQ412" s="1"/>
@@ -31127,7 +31134,7 @@
       <c r="AK413" s="1"/>
       <c r="AL413" s="1"/>
       <c r="AM413" s="1"/>
-      <c r="AN413" s="1"/>
+      <c r="AN413" s="7"/>
       <c r="AO413" s="1"/>
       <c r="AP413" s="1"/>
       <c r="AQ413" s="1"/>
@@ -31177,7 +31184,7 @@
       <c r="AK414" s="1"/>
       <c r="AL414" s="1"/>
       <c r="AM414" s="1"/>
-      <c r="AN414" s="1"/>
+      <c r="AN414" s="7"/>
       <c r="AO414" s="1"/>
       <c r="AP414" s="1"/>
       <c r="AQ414" s="1"/>
@@ -31227,7 +31234,7 @@
       <c r="AK415" s="1"/>
       <c r="AL415" s="1"/>
       <c r="AM415" s="1"/>
-      <c r="AN415" s="1"/>
+      <c r="AN415" s="7"/>
       <c r="AO415" s="1"/>
       <c r="AP415" s="1"/>
       <c r="AQ415" s="1"/>
@@ -31277,7 +31284,7 @@
       <c r="AK416" s="1"/>
       <c r="AL416" s="1"/>
       <c r="AM416" s="1"/>
-      <c r="AN416" s="1"/>
+      <c r="AN416" s="7"/>
       <c r="AO416" s="1"/>
       <c r="AP416" s="1"/>
       <c r="AQ416" s="1"/>
@@ -31327,7 +31334,7 @@
       <c r="AK417" s="1"/>
       <c r="AL417" s="1"/>
       <c r="AM417" s="1"/>
-      <c r="AN417" s="1"/>
+      <c r="AN417" s="7"/>
       <c r="AO417" s="1"/>
       <c r="AP417" s="1"/>
       <c r="AQ417" s="1"/>
@@ -31377,7 +31384,7 @@
       <c r="AK418" s="1"/>
       <c r="AL418" s="1"/>
       <c r="AM418" s="1"/>
-      <c r="AN418" s="1"/>
+      <c r="AN418" s="7"/>
       <c r="AO418" s="1"/>
       <c r="AP418" s="1"/>
       <c r="AQ418" s="1"/>
@@ -31427,7 +31434,7 @@
       <c r="AK419" s="1"/>
       <c r="AL419" s="1"/>
       <c r="AM419" s="1"/>
-      <c r="AN419" s="1"/>
+      <c r="AN419" s="7"/>
       <c r="AO419" s="1"/>
       <c r="AP419" s="1"/>
       <c r="AQ419" s="1"/>
@@ -31477,7 +31484,7 @@
       <c r="AK420" s="1"/>
       <c r="AL420" s="1"/>
       <c r="AM420" s="1"/>
-      <c r="AN420" s="1"/>
+      <c r="AN420" s="7"/>
       <c r="AO420" s="1"/>
       <c r="AP420" s="1"/>
       <c r="AQ420" s="1"/>
@@ -31527,7 +31534,7 @@
       <c r="AK421" s="1"/>
       <c r="AL421" s="1"/>
       <c r="AM421" s="1"/>
-      <c r="AN421" s="1"/>
+      <c r="AN421" s="7"/>
       <c r="AO421" s="1"/>
       <c r="AP421" s="1"/>
       <c r="AQ421" s="1"/>
@@ -31577,7 +31584,7 @@
       <c r="AK422" s="1"/>
       <c r="AL422" s="1"/>
       <c r="AM422" s="1"/>
-      <c r="AN422" s="1"/>
+      <c r="AN422" s="7"/>
       <c r="AO422" s="1"/>
       <c r="AP422" s="1"/>
       <c r="AQ422" s="1"/>
@@ -31627,7 +31634,7 @@
       <c r="AK423" s="1"/>
       <c r="AL423" s="1"/>
       <c r="AM423" s="1"/>
-      <c r="AN423" s="1"/>
+      <c r="AN423" s="7"/>
       <c r="AO423" s="1"/>
       <c r="AP423" s="1"/>
       <c r="AQ423" s="1"/>
@@ -31677,7 +31684,7 @@
       <c r="AK424" s="1"/>
       <c r="AL424" s="1"/>
       <c r="AM424" s="1"/>
-      <c r="AN424" s="1"/>
+      <c r="AN424" s="7"/>
       <c r="AO424" s="1"/>
       <c r="AP424" s="1"/>
       <c r="AQ424" s="1"/>
@@ -31727,7 +31734,7 @@
       <c r="AK425" s="1"/>
       <c r="AL425" s="1"/>
       <c r="AM425" s="1"/>
-      <c r="AN425" s="1"/>
+      <c r="AN425" s="7"/>
       <c r="AO425" s="1"/>
       <c r="AP425" s="1"/>
       <c r="AQ425" s="1"/>
@@ -31777,7 +31784,7 @@
       <c r="AK426" s="1"/>
       <c r="AL426" s="1"/>
       <c r="AM426" s="1"/>
-      <c r="AN426" s="1"/>
+      <c r="AN426" s="7"/>
       <c r="AO426" s="1"/>
       <c r="AP426" s="1"/>
       <c r="AQ426" s="1"/>
@@ -31827,7 +31834,7 @@
       <c r="AK427" s="1"/>
       <c r="AL427" s="1"/>
       <c r="AM427" s="1"/>
-      <c r="AN427" s="1"/>
+      <c r="AN427" s="7"/>
       <c r="AO427" s="1"/>
       <c r="AP427" s="1"/>
       <c r="AQ427" s="1"/>
@@ -31877,7 +31884,7 @@
       <c r="AK428" s="1"/>
       <c r="AL428" s="1"/>
       <c r="AM428" s="1"/>
-      <c r="AN428" s="1"/>
+      <c r="AN428" s="7"/>
       <c r="AO428" s="1"/>
       <c r="AP428" s="1"/>
       <c r="AQ428" s="1"/>
@@ -31927,7 +31934,7 @@
       <c r="AK429" s="1"/>
       <c r="AL429" s="1"/>
       <c r="AM429" s="1"/>
-      <c r="AN429" s="1"/>
+      <c r="AN429" s="7"/>
       <c r="AO429" s="1"/>
       <c r="AP429" s="1"/>
       <c r="AQ429" s="1"/>
@@ -31977,7 +31984,7 @@
       <c r="AK430" s="1"/>
       <c r="AL430" s="1"/>
       <c r="AM430" s="1"/>
-      <c r="AN430" s="1"/>
+      <c r="AN430" s="7"/>
       <c r="AO430" s="1"/>
       <c r="AP430" s="1"/>
       <c r="AQ430" s="1"/>
@@ -32027,7 +32034,7 @@
       <c r="AK431" s="1"/>
       <c r="AL431" s="1"/>
       <c r="AM431" s="1"/>
-      <c r="AN431" s="1"/>
+      <c r="AN431" s="7"/>
       <c r="AO431" s="1"/>
       <c r="AP431" s="1"/>
       <c r="AQ431" s="1"/>
@@ -32077,7 +32084,7 @@
       <c r="AK432" s="1"/>
       <c r="AL432" s="1"/>
       <c r="AM432" s="1"/>
-      <c r="AN432" s="1"/>
+      <c r="AN432" s="7"/>
       <c r="AO432" s="1"/>
       <c r="AP432" s="1"/>
       <c r="AQ432" s="1"/>
@@ -32127,7 +32134,7 @@
       <c r="AK433" s="1"/>
       <c r="AL433" s="1"/>
       <c r="AM433" s="1"/>
-      <c r="AN433" s="1"/>
+      <c r="AN433" s="7"/>
       <c r="AO433" s="1"/>
       <c r="AP433" s="1"/>
       <c r="AQ433" s="1"/>
@@ -32177,7 +32184,7 @@
       <c r="AK434" s="1"/>
       <c r="AL434" s="1"/>
       <c r="AM434" s="1"/>
-      <c r="AN434" s="1"/>
+      <c r="AN434" s="7"/>
       <c r="AO434" s="1"/>
       <c r="AP434" s="1"/>
       <c r="AQ434" s="1"/>
@@ -32227,7 +32234,7 @@
       <c r="AK435" s="1"/>
       <c r="AL435" s="1"/>
       <c r="AM435" s="1"/>
-      <c r="AN435" s="1"/>
+      <c r="AN435" s="7"/>
       <c r="AO435" s="1"/>
       <c r="AP435" s="1"/>
       <c r="AQ435" s="1"/>
@@ -32277,7 +32284,7 @@
       <c r="AK436" s="1"/>
       <c r="AL436" s="1"/>
       <c r="AM436" s="1"/>
-      <c r="AN436" s="1"/>
+      <c r="AN436" s="7"/>
       <c r="AO436" s="1"/>
       <c r="AP436" s="1"/>
       <c r="AQ436" s="1"/>
@@ -32327,7 +32334,7 @@
       <c r="AK437" s="1"/>
       <c r="AL437" s="1"/>
       <c r="AM437" s="1"/>
-      <c r="AN437" s="1"/>
+      <c r="AN437" s="7"/>
       <c r="AO437" s="1"/>
       <c r="AP437" s="1"/>
       <c r="AQ437" s="1"/>
@@ -32377,7 +32384,7 @@
       <c r="AK438" s="1"/>
       <c r="AL438" s="1"/>
       <c r="AM438" s="1"/>
-      <c r="AN438" s="1"/>
+      <c r="AN438" s="7"/>
       <c r="AO438" s="1"/>
       <c r="AP438" s="1"/>
       <c r="AQ438" s="1"/>
@@ -32427,7 +32434,7 @@
       <c r="AK439" s="1"/>
       <c r="AL439" s="1"/>
       <c r="AM439" s="1"/>
-      <c r="AN439" s="1"/>
+      <c r="AN439" s="7"/>
       <c r="AO439" s="1"/>
       <c r="AP439" s="1"/>
       <c r="AQ439" s="1"/>
@@ -32477,7 +32484,7 @@
       <c r="AK440" s="1"/>
       <c r="AL440" s="1"/>
       <c r="AM440" s="1"/>
-      <c r="AN440" s="1"/>
+      <c r="AN440" s="7"/>
       <c r="AO440" s="1"/>
       <c r="AP440" s="1"/>
       <c r="AQ440" s="1"/>
@@ -32527,7 +32534,7 @@
       <c r="AK441" s="1"/>
       <c r="AL441" s="1"/>
       <c r="AM441" s="1"/>
-      <c r="AN441" s="1"/>
+      <c r="AN441" s="7"/>
       <c r="AO441" s="1"/>
       <c r="AP441" s="1"/>
       <c r="AQ441" s="1"/>
@@ -32577,7 +32584,7 @@
       <c r="AK442" s="1"/>
       <c r="AL442" s="1"/>
       <c r="AM442" s="1"/>
-      <c r="AN442" s="1"/>
+      <c r="AN442" s="7"/>
       <c r="AO442" s="1"/>
       <c r="AP442" s="1"/>
       <c r="AQ442" s="1"/>
@@ -32627,7 +32634,7 @@
       <c r="AK443" s="1"/>
       <c r="AL443" s="1"/>
       <c r="AM443" s="1"/>
-      <c r="AN443" s="1"/>
+      <c r="AN443" s="7"/>
       <c r="AO443" s="1"/>
       <c r="AP443" s="1"/>
       <c r="AQ443" s="1"/>
@@ -32677,7 +32684,7 @@
       <c r="AK444" s="1"/>
       <c r="AL444" s="1"/>
       <c r="AM444" s="1"/>
-      <c r="AN444" s="1"/>
+      <c r="AN444" s="7"/>
       <c r="AO444" s="1"/>
       <c r="AP444" s="1"/>
       <c r="AQ444" s="1"/>
@@ -32727,7 +32734,7 @@
       <c r="AK445" s="1"/>
       <c r="AL445" s="1"/>
       <c r="AM445" s="1"/>
-      <c r="AN445" s="1"/>
+      <c r="AN445" s="7"/>
       <c r="AO445" s="1"/>
       <c r="AP445" s="1"/>
       <c r="AQ445" s="1"/>
@@ -32777,7 +32784,7 @@
       <c r="AK446" s="1"/>
       <c r="AL446" s="1"/>
       <c r="AM446" s="1"/>
-      <c r="AN446" s="1"/>
+      <c r="AN446" s="7"/>
       <c r="AO446" s="1"/>
       <c r="AP446" s="1"/>
       <c r="AQ446" s="1"/>
@@ -32827,7 +32834,7 @@
       <c r="AK447" s="1"/>
       <c r="AL447" s="1"/>
       <c r="AM447" s="1"/>
-      <c r="AN447" s="1"/>
+      <c r="AN447" s="7"/>
       <c r="AO447" s="1"/>
       <c r="AP447" s="1"/>
       <c r="AQ447" s="1"/>
@@ -32877,7 +32884,7 @@
       <c r="AK448" s="1"/>
       <c r="AL448" s="1"/>
       <c r="AM448" s="1"/>
-      <c r="AN448" s="1"/>
+      <c r="AN448" s="7"/>
       <c r="AO448" s="1"/>
       <c r="AP448" s="1"/>
       <c r="AQ448" s="1"/>
@@ -32927,7 +32934,7 @@
       <c r="AK449" s="1"/>
       <c r="AL449" s="1"/>
       <c r="AM449" s="1"/>
-      <c r="AN449" s="1"/>
+      <c r="AN449" s="7"/>
       <c r="AO449" s="1"/>
       <c r="AP449" s="1"/>
       <c r="AQ449" s="1"/>
@@ -32977,7 +32984,7 @@
       <c r="AK450" s="1"/>
       <c r="AL450" s="1"/>
       <c r="AM450" s="1"/>
-      <c r="AN450" s="1"/>
+      <c r="AN450" s="7"/>
       <c r="AO450" s="1"/>
       <c r="AP450" s="1"/>
       <c r="AQ450" s="1"/>
@@ -33027,7 +33034,7 @@
       <c r="AK451" s="1"/>
       <c r="AL451" s="1"/>
       <c r="AM451" s="1"/>
-      <c r="AN451" s="1"/>
+      <c r="AN451" s="7"/>
       <c r="AO451" s="1"/>
       <c r="AP451" s="1"/>
       <c r="AQ451" s="1"/>
@@ -33077,7 +33084,7 @@
       <c r="AK452" s="1"/>
       <c r="AL452" s="1"/>
       <c r="AM452" s="1"/>
-      <c r="AN452" s="1"/>
+      <c r="AN452" s="7"/>
       <c r="AO452" s="1"/>
       <c r="AP452" s="1"/>
       <c r="AQ452" s="1"/>
@@ -33127,7 +33134,7 @@
       <c r="AK453" s="1"/>
       <c r="AL453" s="1"/>
       <c r="AM453" s="1"/>
-      <c r="AN453" s="1"/>
+      <c r="AN453" s="7"/>
       <c r="AO453" s="1"/>
       <c r="AP453" s="1"/>
       <c r="AQ453" s="1"/>
@@ -33177,7 +33184,7 @@
       <c r="AK454" s="1"/>
       <c r="AL454" s="1"/>
       <c r="AM454" s="1"/>
-      <c r="AN454" s="1"/>
+      <c r="AN454" s="7"/>
       <c r="AO454" s="1"/>
       <c r="AP454" s="1"/>
       <c r="AQ454" s="1"/>
@@ -33227,7 +33234,7 @@
       <c r="AK455" s="1"/>
       <c r="AL455" s="1"/>
       <c r="AM455" s="1"/>
-      <c r="AN455" s="1"/>
+      <c r="AN455" s="7"/>
       <c r="AO455" s="1"/>
       <c r="AP455" s="1"/>
       <c r="AQ455" s="1"/>
@@ -33277,7 +33284,7 @@
       <c r="AK456" s="1"/>
       <c r="AL456" s="1"/>
       <c r="AM456" s="1"/>
-      <c r="AN456" s="1"/>
+      <c r="AN456" s="7"/>
       <c r="AO456" s="1"/>
       <c r="AP456" s="1"/>
       <c r="AQ456" s="1"/>
@@ -33327,7 +33334,7 @@
       <c r="AK457" s="1"/>
       <c r="AL457" s="1"/>
       <c r="AM457" s="1"/>
-      <c r="AN457" s="1"/>
+      <c r="AN457" s="7"/>
       <c r="AO457" s="1"/>
       <c r="AP457" s="1"/>
       <c r="AQ457" s="1"/>
@@ -33377,7 +33384,7 @@
       <c r="AK458" s="1"/>
       <c r="AL458" s="1"/>
       <c r="AM458" s="1"/>
-      <c r="AN458" s="1"/>
+      <c r="AN458" s="7"/>
       <c r="AO458" s="1"/>
       <c r="AP458" s="1"/>
       <c r="AQ458" s="1"/>
@@ -33427,7 +33434,7 @@
       <c r="AK459" s="1"/>
       <c r="AL459" s="1"/>
       <c r="AM459" s="1"/>
-      <c r="AN459" s="1"/>
+      <c r="AN459" s="7"/>
       <c r="AO459" s="1"/>
       <c r="AP459" s="1"/>
       <c r="AQ459" s="1"/>
@@ -33477,7 +33484,7 @@
       <c r="AK460" s="1"/>
       <c r="AL460" s="1"/>
       <c r="AM460" s="1"/>
-      <c r="AN460" s="1"/>
+      <c r="AN460" s="7"/>
       <c r="AO460" s="1"/>
       <c r="AP460" s="1"/>
       <c r="AQ460" s="1"/>
@@ -33527,7 +33534,7 @@
       <c r="AK461" s="1"/>
       <c r="AL461" s="1"/>
       <c r="AM461" s="1"/>
-      <c r="AN461" s="1"/>
+      <c r="AN461" s="7"/>
       <c r="AO461" s="1"/>
       <c r="AP461" s="1"/>
       <c r="AQ461" s="1"/>
@@ -33577,7 +33584,7 @@
       <c r="AK462" s="1"/>
       <c r="AL462" s="1"/>
       <c r="AM462" s="1"/>
-      <c r="AN462" s="1"/>
+      <c r="AN462" s="7"/>
       <c r="AO462" s="1"/>
       <c r="AP462" s="1"/>
       <c r="AQ462" s="1"/>
@@ -33627,7 +33634,7 @@
       <c r="AK463" s="1"/>
       <c r="AL463" s="1"/>
       <c r="AM463" s="1"/>
-      <c r="AN463" s="1"/>
+      <c r="AN463" s="7"/>
       <c r="AO463" s="1"/>
       <c r="AP463" s="1"/>
       <c r="AQ463" s="1"/>
@@ -33677,7 +33684,7 @@
       <c r="AK464" s="1"/>
       <c r="AL464" s="1"/>
       <c r="AM464" s="1"/>
-      <c r="AN464" s="1"/>
+      <c r="AN464" s="7"/>
       <c r="AO464" s="1"/>
       <c r="AP464" s="1"/>
       <c r="AQ464" s="1"/>
@@ -33727,7 +33734,7 @@
       <c r="AK465" s="1"/>
       <c r="AL465" s="1"/>
       <c r="AM465" s="1"/>
-      <c r="AN465" s="1"/>
+      <c r="AN465" s="7"/>
       <c r="AO465" s="1"/>
       <c r="AP465" s="1"/>
       <c r="AQ465" s="1"/>
@@ -33777,7 +33784,7 @@
       <c r="AK466" s="1"/>
       <c r="AL466" s="1"/>
       <c r="AM466" s="1"/>
-      <c r="AN466" s="1"/>
+      <c r="AN466" s="7"/>
       <c r="AO466" s="1"/>
       <c r="AP466" s="1"/>
       <c r="AQ466" s="1"/>
@@ -33827,7 +33834,7 @@
       <c r="AK467" s="1"/>
       <c r="AL467" s="1"/>
       <c r="AM467" s="1"/>
-      <c r="AN467" s="1"/>
+      <c r="AN467" s="7"/>
       <c r="AO467" s="1"/>
       <c r="AP467" s="1"/>
       <c r="AQ467" s="1"/>
@@ -33877,7 +33884,7 @@
       <c r="AK468" s="1"/>
       <c r="AL468" s="1"/>
       <c r="AM468" s="1"/>
-      <c r="AN468" s="1"/>
+      <c r="AN468" s="7"/>
       <c r="AO468" s="1"/>
       <c r="AP468" s="1"/>
       <c r="AQ468" s="1"/>
@@ -33927,7 +33934,7 @@
       <c r="AK469" s="1"/>
       <c r="AL469" s="1"/>
       <c r="AM469" s="1"/>
-      <c r="AN469" s="1"/>
+      <c r="AN469" s="7"/>
       <c r="AO469" s="1"/>
       <c r="AP469" s="1"/>
       <c r="AQ469" s="1"/>
@@ -33977,7 +33984,7 @@
       <c r="AK470" s="1"/>
       <c r="AL470" s="1"/>
       <c r="AM470" s="1"/>
-      <c r="AN470" s="1"/>
+      <c r="AN470" s="7"/>
       <c r="AO470" s="1"/>
       <c r="AP470" s="1"/>
       <c r="AQ470" s="1"/>
@@ -34027,7 +34034,7 @@
       <c r="AK471" s="1"/>
       <c r="AL471" s="1"/>
       <c r="AM471" s="1"/>
-      <c r="AN471" s="1"/>
+      <c r="AN471" s="7"/>
       <c r="AO471" s="1"/>
       <c r="AP471" s="1"/>
       <c r="AQ471" s="1"/>
@@ -34077,7 +34084,7 @@
       <c r="AK472" s="1"/>
       <c r="AL472" s="1"/>
       <c r="AM472" s="1"/>
-      <c r="AN472" s="1"/>
+      <c r="AN472" s="7"/>
       <c r="AO472" s="1"/>
       <c r="AP472" s="1"/>
       <c r="AQ472" s="1"/>
@@ -34127,7 +34134,7 @@
       <c r="AK473" s="1"/>
       <c r="AL473" s="1"/>
       <c r="AM473" s="1"/>
-      <c r="AN473" s="1"/>
+      <c r="AN473" s="7"/>
       <c r="AO473" s="1"/>
       <c r="AP473" s="1"/>
       <c r="AQ473" s="1"/>
@@ -34177,7 +34184,7 @@
       <c r="AK474" s="1"/>
       <c r="AL474" s="1"/>
       <c r="AM474" s="1"/>
-      <c r="AN474" s="1"/>
+      <c r="AN474" s="7"/>
       <c r="AO474" s="1"/>
       <c r="AP474" s="1"/>
       <c r="AQ474" s="1"/>
@@ -34227,7 +34234,7 @@
       <c r="AK475" s="1"/>
       <c r="AL475" s="1"/>
       <c r="AM475" s="1"/>
-      <c r="AN475" s="1"/>
+      <c r="AN475" s="7"/>
       <c r="AO475" s="1"/>
       <c r="AP475" s="1"/>
       <c r="AQ475" s="1"/>
@@ -34277,7 +34284,7 @@
       <c r="AK476" s="1"/>
       <c r="AL476" s="1"/>
       <c r="AM476" s="1"/>
-      <c r="AN476" s="1"/>
+      <c r="AN476" s="7"/>
       <c r="AO476" s="1"/>
       <c r="AP476" s="1"/>
       <c r="AQ476" s="1"/>
@@ -34327,7 +34334,7 @@
       <c r="AK477" s="1"/>
       <c r="AL477" s="1"/>
       <c r="AM477" s="1"/>
-      <c r="AN477" s="1"/>
+      <c r="AN477" s="7"/>
       <c r="AO477" s="1"/>
       <c r="AP477" s="1"/>
       <c r="AQ477" s="1"/>
@@ -34377,7 +34384,7 @@
       <c r="AK478" s="1"/>
       <c r="AL478" s="1"/>
       <c r="AM478" s="1"/>
-      <c r="AN478" s="1"/>
+      <c r="AN478" s="7"/>
       <c r="AO478" s="1"/>
       <c r="AP478" s="1"/>
       <c r="AQ478" s="1"/>
@@ -34427,7 +34434,7 @@
       <c r="AK479" s="1"/>
       <c r="AL479" s="1"/>
       <c r="AM479" s="1"/>
-      <c r="AN479" s="1"/>
+      <c r="AN479" s="7"/>
       <c r="AO479" s="1"/>
       <c r="AP479" s="1"/>
       <c r="AQ479" s="1"/>
@@ -34477,7 +34484,7 @@
       <c r="AK480" s="1"/>
       <c r="AL480" s="1"/>
       <c r="AM480" s="1"/>
-      <c r="AN480" s="1"/>
+      <c r="AN480" s="7"/>
       <c r="AO480" s="1"/>
       <c r="AP480" s="1"/>
       <c r="AQ480" s="1"/>
@@ -34527,7 +34534,7 @@
       <c r="AK481" s="1"/>
       <c r="AL481" s="1"/>
       <c r="AM481" s="1"/>
-      <c r="AN481" s="1"/>
+      <c r="AN481" s="7"/>
       <c r="AO481" s="1"/>
       <c r="AP481" s="1"/>
       <c r="AQ481" s="1"/>
@@ -34577,7 +34584,7 @@
       <c r="AK482" s="1"/>
       <c r="AL482" s="1"/>
       <c r="AM482" s="1"/>
-      <c r="AN482" s="1"/>
+      <c r="AN482" s="7"/>
       <c r="AO482" s="1"/>
       <c r="AP482" s="1"/>
       <c r="AQ482" s="1"/>
@@ -34627,7 +34634,7 @@
       <c r="AK483" s="1"/>
       <c r="AL483" s="1"/>
       <c r="AM483" s="1"/>
-      <c r="AN483" s="1"/>
+      <c r="AN483" s="7"/>
       <c r="AO483" s="1"/>
       <c r="AP483" s="1"/>
       <c r="AQ483" s="1"/>
@@ -34677,7 +34684,7 @@
       <c r="AK484" s="1"/>
       <c r="AL484" s="1"/>
       <c r="AM484" s="1"/>
-      <c r="AN484" s="1"/>
+      <c r="AN484" s="7"/>
       <c r="AO484" s="1"/>
       <c r="AP484" s="1"/>
       <c r="AQ484" s="1"/>
@@ -34727,7 +34734,7 @@
       <c r="AK485" s="1"/>
       <c r="AL485" s="1"/>
       <c r="AM485" s="1"/>
-      <c r="AN485" s="1"/>
+      <c r="AN485" s="7"/>
       <c r="AO485" s="1"/>
       <c r="AP485" s="1"/>
       <c r="AQ485" s="1"/>
@@ -34777,7 +34784,7 @@
       <c r="AK486" s="1"/>
       <c r="AL486" s="1"/>
       <c r="AM486" s="1"/>
-      <c r="AN486" s="1"/>
+      <c r="AN486" s="7"/>
       <c r="AO486" s="1"/>
       <c r="AP486" s="1"/>
       <c r="AQ486" s="1"/>
@@ -34827,7 +34834,7 @@
       <c r="AK487" s="1"/>
       <c r="AL487" s="1"/>
       <c r="AM487" s="1"/>
-      <c r="AN487" s="1"/>
+      <c r="AN487" s="7"/>
       <c r="AO487" s="1"/>
       <c r="AP487" s="1"/>
       <c r="AQ487" s="1"/>
@@ -34877,7 +34884,7 @@
       <c r="AK488" s="1"/>
       <c r="AL488" s="1"/>
       <c r="AM488" s="1"/>
-      <c r="AN488" s="1"/>
+      <c r="AN488" s="7"/>
       <c r="AO488" s="1"/>
       <c r="AP488" s="1"/>
       <c r="AQ488" s="1"/>
@@ -34927,7 +34934,7 @@
       <c r="AK489" s="1"/>
       <c r="AL489" s="1"/>
       <c r="AM489" s="1"/>
-      <c r="AN489" s="1"/>
+      <c r="AN489" s="7"/>
       <c r="AO489" s="1"/>
       <c r="AP489" s="1"/>
       <c r="AQ489" s="1"/>
@@ -34977,7 +34984,7 @@
       <c r="AK490" s="1"/>
       <c r="AL490" s="1"/>
       <c r="AM490" s="1"/>
-      <c r="AN490" s="1"/>
+      <c r="AN490" s="7"/>
       <c r="AO490" s="1"/>
       <c r="AP490" s="1"/>
       <c r="AQ490" s="1"/>
@@ -35027,7 +35034,7 @@
       <c r="AK491" s="1"/>
       <c r="AL491" s="1"/>
       <c r="AM491" s="1"/>
-      <c r="AN491" s="1"/>
+      <c r="AN491" s="7"/>
       <c r="AO491" s="1"/>
       <c r="AP491" s="1"/>
       <c r="AQ491" s="1"/>
@@ -35077,7 +35084,7 @@
       <c r="AK492" s="1"/>
       <c r="AL492" s="1"/>
       <c r="AM492" s="1"/>
-      <c r="AN492" s="1"/>
+      <c r="AN492" s="7"/>
       <c r="AO492" s="1"/>
       <c r="AP492" s="1"/>
       <c r="AQ492" s="1"/>
@@ -35127,7 +35134,7 @@
       <c r="AK493" s="1"/>
       <c r="AL493" s="1"/>
       <c r="AM493" s="1"/>
-      <c r="AN493" s="1"/>
+      <c r="AN493" s="7"/>
       <c r="AO493" s="1"/>
       <c r="AP493" s="1"/>
       <c r="AQ493" s="1"/>
@@ -35177,7 +35184,7 @@
       <c r="AK494" s="1"/>
       <c r="AL494" s="1"/>
       <c r="AM494" s="1"/>
-      <c r="AN494" s="1"/>
+      <c r="AN494" s="7"/>
       <c r="AO494" s="1"/>
       <c r="AP494" s="1"/>
       <c r="AQ494" s="1"/>
@@ -35227,7 +35234,7 @@
       <c r="AK495" s="1"/>
       <c r="AL495" s="1"/>
       <c r="AM495" s="1"/>
-      <c r="AN495" s="1"/>
+      <c r="AN495" s="7"/>
       <c r="AO495" s="1"/>
       <c r="AP495" s="1"/>
       <c r="AQ495" s="1"/>
@@ -35277,7 +35284,7 @@
       <c r="AK496" s="1"/>
       <c r="AL496" s="1"/>
       <c r="AM496" s="1"/>
-      <c r="AN496" s="1"/>
+      <c r="AN496" s="7"/>
       <c r="AO496" s="1"/>
       <c r="AP496" s="1"/>
       <c r="AQ496" s="1"/>
